--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -1248,7 +1248,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131222821</v>
+        <v>131223136</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1279,7 +1279,12 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1288,13 +1293,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449374</v>
+        <v>449315</v>
       </c>
       <c r="R6" t="n">
-        <v>6999458</v>
+        <v>6999445</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1323,7 +1328,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1333,12 +1338,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1390,7 +1395,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131223136</v>
+        <v>131222821</v>
       </c>
       <c r="B7" t="n">
         <v>57884</v>
@@ -1421,12 +1426,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449315</v>
+        <v>449374</v>
       </c>
       <c r="R7" t="n">
-        <v>6999445</v>
+        <v>6999458</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1824,40 +1824,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131231421</v>
+        <v>131231403</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>92531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1867,10 +1866,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449687</v>
+        <v>449444</v>
       </c>
       <c r="R10" t="n">
-        <v>6999537</v>
+        <v>6999489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1905,17 +1904,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1934,14 +1929,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2089,39 +2079,40 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131231403</v>
+        <v>131231421</v>
       </c>
       <c r="B12" t="n">
-        <v>92531</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2131,10 +2122,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449444</v>
+        <v>449687</v>
       </c>
       <c r="R12" t="n">
-        <v>6999489</v>
+        <v>6999537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2169,13 +2160,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2194,9 +2189,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2476,7 +2476,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131231418</v>
+        <v>131231413</v>
       </c>
       <c r="B15" t="n">
         <v>57884</v>
@@ -2509,7 +2509,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449617</v>
+        <v>449388</v>
       </c>
       <c r="R15" t="n">
-        <v>6999646</v>
+        <v>6999459</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2586,9 +2586,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2606,7 +2611,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131231413</v>
+        <v>131231418</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2639,7 +2644,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2649,10 +2654,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449388</v>
+        <v>449617</v>
       </c>
       <c r="R16" t="n">
-        <v>6999459</v>
+        <v>6999646</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2689,7 +2694,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2716,14 +2721,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131231417</v>
+        <v>131231274</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4169,29 +4169,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4201,10 +4196,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449423</v>
+        <v>449562</v>
       </c>
       <c r="R28" t="n">
-        <v>6999465</v>
+        <v>6999557</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4241,7 +4236,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4250,6 +4245,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4268,9 +4264,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4288,10 +4289,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131231274</v>
+        <v>131231417</v>
       </c>
       <c r="B29" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4299,24 +4300,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4326,10 +4332,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449562</v>
+        <v>449423</v>
       </c>
       <c r="R29" t="n">
-        <v>6999557</v>
+        <v>6999465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4366,7 +4372,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4375,7 +4381,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4394,14 +4399,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131231469</v>
+        <v>131231416</v>
       </c>
       <c r="B30" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4430,26 +4430,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4457,10 +4462,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449689</v>
+        <v>449456</v>
       </c>
       <c r="R30" t="n">
-        <v>6999668</v>
+        <v>6999484</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4497,7 +4502,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Växer här på sälg.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4506,7 +4511,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4517,22 +4521,17 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4676,10 +4675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131231275</v>
+        <v>131231469</v>
       </c>
       <c r="B32" t="n">
-        <v>79244</v>
+        <v>80349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4687,21 +4686,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4714,10 +4713,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449233</v>
+        <v>449689</v>
       </c>
       <c r="R32" t="n">
-        <v>6999424</v>
+        <v>6999668</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4752,6 +4751,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Växer här på sälg.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4769,22 +4773,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4802,10 +4806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131231416</v>
+        <v>131231275</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4813,31 +4817,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4845,10 +4844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449456</v>
+        <v>449233</v>
       </c>
       <c r="R33" t="n">
-        <v>6999484</v>
+        <v>6999424</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4883,17 +4882,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4912,9 +4907,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -1684,39 +1684,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131231273</v>
+        <v>131231403</v>
       </c>
       <c r="B9" t="n">
-        <v>80349</v>
+        <v>92531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449640</v>
+        <v>449444</v>
       </c>
       <c r="R9" t="n">
-        <v>6999605</v>
+        <v>6999489</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1764,11 +1764,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1784,29 +1779,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1824,39 +1809,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131231403</v>
+        <v>131231420</v>
       </c>
       <c r="B10" t="n">
-        <v>92531</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1866,10 +1852,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449444</v>
+        <v>449719</v>
       </c>
       <c r="R10" t="n">
-        <v>6999489</v>
+        <v>6999549</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1904,13 +1890,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1949,7 +1939,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131231420</v>
+        <v>131231421</v>
       </c>
       <c r="B11" t="n">
         <v>57884</v>
@@ -1992,10 +1982,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449719</v>
+        <v>449687</v>
       </c>
       <c r="R11" t="n">
-        <v>6999549</v>
+        <v>6999537</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2059,9 +2049,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2079,10 +2074,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131231421</v>
+        <v>131231273</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>80349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2090,29 +2085,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2122,10 +2116,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449687</v>
+        <v>449640</v>
       </c>
       <c r="R12" t="n">
-        <v>6999537</v>
+        <v>6999605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2162,7 +2156,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2171,6 +2165,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2179,24 +2174,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131231401</v>
+        <v>131231281</v>
       </c>
       <c r="B24" t="n">
-        <v>91809</v>
+        <v>79244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3662,30 +3662,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3693,10 +3689,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449639</v>
+        <v>449569</v>
       </c>
       <c r="R24" t="n">
-        <v>6999626</v>
+        <v>6999561</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3731,6 +3727,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3756,9 +3757,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3776,10 +3782,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131231399</v>
+        <v>131231282</v>
       </c>
       <c r="B25" t="n">
-        <v>91809</v>
+        <v>79244</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3787,30 +3793,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3818,10 +3820,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449456</v>
+        <v>449559</v>
       </c>
       <c r="R25" t="n">
-        <v>6999489</v>
+        <v>6999502</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3881,9 +3883,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3901,10 +3908,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131231281</v>
+        <v>131231401</v>
       </c>
       <c r="B26" t="n">
-        <v>79244</v>
+        <v>91809</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3912,26 +3919,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3939,10 +3950,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449569</v>
+        <v>449639</v>
       </c>
       <c r="R26" t="n">
-        <v>6999561</v>
+        <v>6999626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3977,11 +3988,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4007,14 +4013,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4032,10 +4033,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131231282</v>
+        <v>131231399</v>
       </c>
       <c r="B27" t="n">
-        <v>79244</v>
+        <v>91809</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4043,26 +4044,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4070,10 +4075,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449559</v>
+        <v>449456</v>
       </c>
       <c r="R27" t="n">
-        <v>6999502</v>
+        <v>6999489</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4133,14 +4138,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131231416</v>
+        <v>131231275</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4430,31 +4430,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4462,10 +4457,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449456</v>
+        <v>449233</v>
       </c>
       <c r="R30" t="n">
-        <v>6999484</v>
+        <v>6999424</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4500,17 +4495,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4529,9 +4520,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4806,10 +4802,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131231275</v>
+        <v>131231416</v>
       </c>
       <c r="B33" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4817,26 +4813,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4844,10 +4845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449233</v>
+        <v>449456</v>
       </c>
       <c r="R33" t="n">
-        <v>6999424</v>
+        <v>6999484</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4882,13 +4883,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4907,14 +4912,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131222457</v>
+        <v>131231430</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4943,47 +4943,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åmyren, Åmyren, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449779</v>
+        <v>449758</v>
       </c>
       <c r="R34" t="n">
-        <v>6999560</v>
+        <v>6999616</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5010,24 +5003,14 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5036,6 +5019,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5056,12 +5040,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5079,10 +5063,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131231430</v>
+        <v>131222457</v>
       </c>
       <c r="B35" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5090,40 +5074,47 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449758</v>
+        <v>449779</v>
       </c>
       <c r="R35" t="n">
-        <v>6999616</v>
+        <v>6999560</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5150,14 +5141,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med garnlavsbålar.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5166,7 +5167,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131231402</v>
+        <v>131231414</v>
       </c>
       <c r="B37" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5347,28 +5347,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5378,10 +5379,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449563</v>
+        <v>449386</v>
       </c>
       <c r="R37" t="n">
-        <v>6999529</v>
+        <v>6999458</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5416,13 +5417,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5461,10 +5466,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131231414</v>
+        <v>131231402</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5472,29 +5477,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5504,10 +5508,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>449386</v>
+        <v>449563</v>
       </c>
       <c r="R38" t="n">
-        <v>6999458</v>
+        <v>6999529</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5542,17 +5546,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131231422</v>
+        <v>131231429</v>
       </c>
       <c r="B41" t="n">
-        <v>58043</v>
+        <v>79244</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5853,50 +5853,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449519</v>
+        <v>449725</v>
       </c>
       <c r="R41" t="n">
-        <v>6999620</v>
+        <v>6999697</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5933,7 +5920,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5942,6 +5929,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5950,9 +5938,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Med inslag av björk och sälg.</t>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5970,7 +5973,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131231429</v>
+        <v>131231471</v>
       </c>
       <c r="B42" t="n">
         <v>79244</v>
@@ -6008,10 +6011,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449725</v>
+        <v>449735</v>
       </c>
       <c r="R42" t="n">
-        <v>6999697</v>
+        <v>6999573</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6044,11 +6047,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6101,10 +6099,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131231471</v>
+        <v>131231470</v>
       </c>
       <c r="B43" t="n">
-        <v>79244</v>
+        <v>91829</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6112,26 +6110,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6139,10 +6137,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449735</v>
+        <v>449620</v>
       </c>
       <c r="R43" t="n">
-        <v>6999573</v>
+        <v>6999568</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6202,14 +6200,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6227,10 +6220,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131231470</v>
+        <v>131231422</v>
       </c>
       <c r="B44" t="n">
-        <v>91829</v>
+        <v>58043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6238,37 +6231,50 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449620</v>
+        <v>449519</v>
       </c>
       <c r="R44" t="n">
-        <v>6999568</v>
+        <v>6999620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6303,13 +6309,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6318,19 +6328,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Med inslag av björk och sälg.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131223307</v>
       </c>
       <c r="B2" t="n">
-        <v>92531</v>
+        <v>92532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>131222541</v>
       </c>
       <c r="B5" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1684,39 +1684,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131231403</v>
+        <v>131231420</v>
       </c>
       <c r="B9" t="n">
-        <v>92531</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1726,10 +1727,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449444</v>
+        <v>449719</v>
       </c>
       <c r="R9" t="n">
-        <v>6999489</v>
+        <v>6999549</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1764,13 +1765,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1809,7 +1814,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131231420</v>
+        <v>131231421</v>
       </c>
       <c r="B10" t="n">
         <v>57884</v>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449719</v>
+        <v>449687</v>
       </c>
       <c r="R10" t="n">
-        <v>6999549</v>
+        <v>6999537</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1919,9 +1924,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1939,10 +1949,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131231421</v>
+        <v>131231273</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>80350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1950,29 +1960,28 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1982,10 +1991,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449687</v>
+        <v>449640</v>
       </c>
       <c r="R11" t="n">
-        <v>6999537</v>
+        <v>6999605</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2022,7 +2031,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2031,6 +2040,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2039,24 +2049,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2074,39 +2089,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131231273</v>
+        <v>131231403</v>
       </c>
       <c r="B12" t="n">
-        <v>80349</v>
+        <v>92532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2116,10 +2131,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449640</v>
+        <v>449444</v>
       </c>
       <c r="R12" t="n">
-        <v>6999605</v>
+        <v>6999489</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2154,11 +2169,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2174,29 +2184,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131231276</v>
+        <v>131231277</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449610</v>
+        <v>449771</v>
       </c>
       <c r="R13" t="n">
-        <v>6999650</v>
+        <v>6999558</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gott om garnlav på flera granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2345,10 +2345,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131231277</v>
+        <v>131231276</v>
       </c>
       <c r="B14" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449771</v>
+        <v>449610</v>
       </c>
       <c r="R14" t="n">
-        <v>6999558</v>
+        <v>6999650</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Gott om garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2741,10 +2741,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131231272</v>
+        <v>131231279</v>
       </c>
       <c r="B17" t="n">
-        <v>80350</v>
+        <v>79245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2752,21 +2752,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449248</v>
+        <v>449722</v>
       </c>
       <c r="R17" t="n">
-        <v>6999432</v>
+        <v>6999656</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2837,29 +2837,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2877,10 +2872,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131231464</v>
+        <v>131231272</v>
       </c>
       <c r="B18" t="n">
-        <v>91809</v>
+        <v>80351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,30 +2883,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2919,10 +2910,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449494</v>
+        <v>449248</v>
       </c>
       <c r="R18" t="n">
-        <v>6999520</v>
+        <v>6999432</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2957,6 +2948,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2972,19 +2968,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3002,10 +3008,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131231279</v>
+        <v>131231464</v>
       </c>
       <c r="B19" t="n">
-        <v>79244</v>
+        <v>91810</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3013,26 +3019,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3040,10 +3050,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449722</v>
+        <v>449494</v>
       </c>
       <c r="R19" t="n">
-        <v>6999656</v>
+        <v>6999520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3078,11 +3088,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3108,14 +3113,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3136,7 +3136,7 @@
         <v>131231426</v>
       </c>
       <c r="B20" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131231280</v>
+        <v>131231278</v>
       </c>
       <c r="B21" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449639</v>
+        <v>449763</v>
       </c>
       <c r="R21" t="n">
-        <v>6999579</v>
+        <v>6999609</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gott om garnlavsbålar på flera gamla granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3385,10 +3385,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131231278</v>
+        <v>131231280</v>
       </c>
       <c r="B22" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449763</v>
+        <v>449639</v>
       </c>
       <c r="R22" t="n">
-        <v>6999609</v>
+        <v>6999579</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Gott om garnlavsbålar på flera gamla granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131231281</v>
+        <v>131231282</v>
       </c>
       <c r="B24" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449569</v>
+        <v>449559</v>
       </c>
       <c r="R24" t="n">
-        <v>6999561</v>
+        <v>6999502</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3725,11 +3725,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3782,10 +3777,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131231282</v>
+        <v>131231281</v>
       </c>
       <c r="B25" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3820,10 +3815,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449559</v>
+        <v>449569</v>
       </c>
       <c r="R25" t="n">
-        <v>6999502</v>
+        <v>6999561</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3856,6 +3851,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3908,10 +3908,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131231401</v>
+        <v>131231399</v>
       </c>
       <c r="B26" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449639</v>
+        <v>449456</v>
       </c>
       <c r="R26" t="n">
-        <v>6999626</v>
+        <v>6999489</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4033,10 +4033,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131231399</v>
+        <v>131231401</v>
       </c>
       <c r="B27" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4075,10 +4075,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449456</v>
+        <v>449639</v>
       </c>
       <c r="R27" t="n">
-        <v>6999489</v>
+        <v>6999626</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4161,7 +4161,7 @@
         <v>131231274</v>
       </c>
       <c r="B28" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>131231275</v>
       </c>
       <c r="B30" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4548,7 +4548,7 @@
         <v>131231424</v>
       </c>
       <c r="B31" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>131231469</v>
       </c>
       <c r="B32" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>131231430</v>
       </c>
       <c r="B34" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>131231425</v>
       </c>
       <c r="B36" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>131231402</v>
       </c>
       <c r="B38" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>131231400</v>
       </c>
       <c r="B39" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>131231423</v>
       </c>
       <c r="B40" t="n">
-        <v>79403</v>
+        <v>79404</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>131231429</v>
       </c>
       <c r="B41" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>131231471</v>
       </c>
       <c r="B42" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>131231470</v>
       </c>
       <c r="B43" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -1949,39 +1949,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131231273</v>
+        <v>131231403</v>
       </c>
       <c r="B11" t="n">
-        <v>80350</v>
+        <v>92532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449640</v>
+        <v>449444</v>
       </c>
       <c r="R11" t="n">
-        <v>6999605</v>
+        <v>6999489</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2029,11 +2029,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -2049,29 +2044,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2089,39 +2074,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131231403</v>
+        <v>131231273</v>
       </c>
       <c r="B12" t="n">
-        <v>92532</v>
+        <v>80350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2131,10 +2116,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449444</v>
+        <v>449640</v>
       </c>
       <c r="R12" t="n">
-        <v>6999489</v>
+        <v>6999605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2169,6 +2154,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2184,19 +2174,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131231274</v>
+        <v>131231417</v>
       </c>
       <c r="B28" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4169,24 +4169,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4196,10 +4201,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449562</v>
+        <v>449423</v>
       </c>
       <c r="R28" t="n">
-        <v>6999557</v>
+        <v>6999465</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4236,7 +4241,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4245,7 +4250,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4264,14 +4268,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4289,10 +4288,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131231417</v>
+        <v>131231274</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4300,29 +4299,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4332,10 +4326,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449423</v>
+        <v>449562</v>
       </c>
       <c r="R29" t="n">
-        <v>6999465</v>
+        <v>6999557</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4372,7 +4366,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4381,6 +4375,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4399,9 +4394,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131231417</v>
+        <v>131231274</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4169,29 +4169,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4201,10 +4196,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449423</v>
+        <v>449562</v>
       </c>
       <c r="R28" t="n">
-        <v>6999465</v>
+        <v>6999557</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4241,7 +4236,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4250,6 +4245,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4268,9 +4264,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4288,10 +4289,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131231274</v>
+        <v>131231417</v>
       </c>
       <c r="B29" t="n">
-        <v>91830</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4299,24 +4300,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4326,10 +4332,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449562</v>
+        <v>449423</v>
       </c>
       <c r="R29" t="n">
-        <v>6999557</v>
+        <v>6999465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4366,7 +4372,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4375,7 +4381,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4394,14 +4399,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131231429</v>
+        <v>131231422</v>
       </c>
       <c r="B41" t="n">
-        <v>79245</v>
+        <v>58043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5853,37 +5853,50 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449725</v>
+        <v>449519</v>
       </c>
       <c r="R41" t="n">
-        <v>6999697</v>
+        <v>6999620</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5920,7 +5933,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt med garnlavsbålar.</t>
+          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5929,7 +5942,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5938,24 +5950,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Med inslag av björk och sälg.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5973,7 +5970,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131231471</v>
+        <v>131231429</v>
       </c>
       <c r="B42" t="n">
         <v>79245</v>
@@ -6011,10 +6008,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449735</v>
+        <v>449725</v>
       </c>
       <c r="R42" t="n">
-        <v>6999573</v>
+        <v>6999697</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6047,6 +6044,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6099,10 +6101,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131231470</v>
+        <v>131231471</v>
       </c>
       <c r="B43" t="n">
-        <v>91830</v>
+        <v>79245</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6110,26 +6112,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6137,10 +6139,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449620</v>
+        <v>449735</v>
       </c>
       <c r="R43" t="n">
-        <v>6999568</v>
+        <v>6999573</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6200,9 +6202,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6220,10 +6227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131231422</v>
+        <v>131231470</v>
       </c>
       <c r="B44" t="n">
-        <v>58043</v>
+        <v>91830</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6231,50 +6238,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449519</v>
+        <v>449620</v>
       </c>
       <c r="R44" t="n">
-        <v>6999620</v>
+        <v>6999568</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6309,17 +6303,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6328,9 +6318,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Med inslag av björk och sälg.</t>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131223307</v>
       </c>
       <c r="B2" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131231420</v>
+        <v>131231273</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>80350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1695,29 +1695,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1727,10 +1726,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449719</v>
+        <v>449640</v>
       </c>
       <c r="R9" t="n">
-        <v>6999549</v>
+        <v>6999605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1767,7 +1766,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1776,6 +1775,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1784,19 +1784,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1814,40 +1824,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131231421</v>
+        <v>131231403</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>92535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1857,10 +1866,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449687</v>
+        <v>449444</v>
       </c>
       <c r="R10" t="n">
-        <v>6999537</v>
+        <v>6999489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1895,17 +1904,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1924,14 +1929,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1949,39 +1949,40 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131231403</v>
+        <v>131231420</v>
       </c>
       <c r="B11" t="n">
-        <v>92532</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1991,10 +1992,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449444</v>
+        <v>449719</v>
       </c>
       <c r="R11" t="n">
-        <v>6999489</v>
+        <v>6999549</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2029,13 +2030,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2074,10 +2079,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131231273</v>
+        <v>131231421</v>
       </c>
       <c r="B12" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2085,28 +2090,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2116,10 +2122,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449640</v>
+        <v>449687</v>
       </c>
       <c r="R12" t="n">
-        <v>6999605</v>
+        <v>6999537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2156,7 +2162,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2165,7 +2171,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2174,29 +2179,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131231277</v>
+        <v>131231276</v>
       </c>
       <c r="B13" t="n">
         <v>79245</v>
@@ -2252,10 +2252,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449771</v>
+        <v>449610</v>
       </c>
       <c r="R13" t="n">
-        <v>6999558</v>
+        <v>6999650</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Gott om garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2345,7 +2345,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131231276</v>
+        <v>131231277</v>
       </c>
       <c r="B14" t="n">
         <v>79245</v>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449610</v>
+        <v>449771</v>
       </c>
       <c r="R14" t="n">
-        <v>6999650</v>
+        <v>6999558</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gott om garnlav på flera granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2741,10 +2741,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131231279</v>
+        <v>131231272</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>80351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2752,21 +2752,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449722</v>
+        <v>449248</v>
       </c>
       <c r="R17" t="n">
-        <v>6999656</v>
+        <v>6999432</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2837,24 +2837,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2872,10 +2877,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131231272</v>
+        <v>131231464</v>
       </c>
       <c r="B18" t="n">
-        <v>80351</v>
+        <v>91813</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2883,26 +2888,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2910,10 +2919,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449248</v>
+        <v>449494</v>
       </c>
       <c r="R18" t="n">
-        <v>6999432</v>
+        <v>6999520</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2948,11 +2957,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2968,29 +2972,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3008,10 +3002,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131231464</v>
+        <v>131231279</v>
       </c>
       <c r="B19" t="n">
-        <v>91810</v>
+        <v>79245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3019,30 +3013,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3050,10 +3040,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449494</v>
+        <v>449722</v>
       </c>
       <c r="R19" t="n">
-        <v>6999520</v>
+        <v>6999656</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3088,6 +3078,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3113,9 +3108,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3136,7 +3136,7 @@
         <v>131231426</v>
       </c>
       <c r="B20" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131231278</v>
+        <v>131231280</v>
       </c>
       <c r="B21" t="n">
         <v>79245</v>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449763</v>
+        <v>449639</v>
       </c>
       <c r="R21" t="n">
-        <v>6999609</v>
+        <v>6999579</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Gott om garnlavsbålar på flera gamla granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3385,7 +3385,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131231280</v>
+        <v>131231278</v>
       </c>
       <c r="B22" t="n">
         <v>79245</v>
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449639</v>
+        <v>449763</v>
       </c>
       <c r="R22" t="n">
-        <v>6999579</v>
+        <v>6999609</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gott om garnlavsbålar på flera gamla granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3651,10 +3651,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131231282</v>
+        <v>131231401</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>91813</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3662,26 +3662,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3689,10 +3693,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449559</v>
+        <v>449639</v>
       </c>
       <c r="R24" t="n">
-        <v>6999502</v>
+        <v>6999626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3752,14 +3756,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3908,10 +3907,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131231399</v>
+        <v>131231282</v>
       </c>
       <c r="B26" t="n">
-        <v>91810</v>
+        <v>79245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3919,30 +3918,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3950,10 +3945,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449456</v>
+        <v>449559</v>
       </c>
       <c r="R26" t="n">
-        <v>6999489</v>
+        <v>6999502</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4013,9 +4008,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131231401</v>
+        <v>131231399</v>
       </c>
       <c r="B27" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4075,10 +4075,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449639</v>
+        <v>449456</v>
       </c>
       <c r="R27" t="n">
-        <v>6999626</v>
+        <v>6999489</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4161,7 +4161,7 @@
         <v>131231274</v>
       </c>
       <c r="B28" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131231430</v>
+        <v>131222457</v>
       </c>
       <c r="B34" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4943,40 +4943,47 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449758</v>
+        <v>449779</v>
       </c>
       <c r="R34" t="n">
-        <v>6999616</v>
+        <v>6999560</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5003,14 +5010,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med garnlavsbålar.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5019,7 +5036,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5040,12 +5056,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5063,10 +5079,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131222457</v>
+        <v>131231430</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5074,47 +5090,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åmyren, Åmyren, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449779</v>
+        <v>449758</v>
       </c>
       <c r="R35" t="n">
-        <v>6999560</v>
+        <v>6999616</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5141,24 +5150,14 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5167,6 +5166,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5213,7 +5213,7 @@
         <v>131231425</v>
       </c>
       <c r="B36" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>131231402</v>
       </c>
       <c r="B38" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>131231400</v>
       </c>
       <c r="B39" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131231422</v>
+        <v>131231429</v>
       </c>
       <c r="B41" t="n">
-        <v>58043</v>
+        <v>79245</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5853,50 +5853,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449519</v>
+        <v>449725</v>
       </c>
       <c r="R41" t="n">
-        <v>6999620</v>
+        <v>6999697</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5933,7 +5920,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5942,6 +5929,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5950,9 +5938,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Med inslag av björk och sälg.</t>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5970,7 +5973,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131231429</v>
+        <v>131231471</v>
       </c>
       <c r="B42" t="n">
         <v>79245</v>
@@ -6008,10 +6011,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449725</v>
+        <v>449735</v>
       </c>
       <c r="R42" t="n">
-        <v>6999697</v>
+        <v>6999573</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6044,11 +6047,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6101,10 +6099,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131231471</v>
+        <v>131231470</v>
       </c>
       <c r="B43" t="n">
-        <v>79245</v>
+        <v>91833</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6112,26 +6110,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6139,10 +6137,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449735</v>
+        <v>449620</v>
       </c>
       <c r="R43" t="n">
-        <v>6999573</v>
+        <v>6999568</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6202,14 +6200,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6227,10 +6220,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131231470</v>
+        <v>131231422</v>
       </c>
       <c r="B44" t="n">
-        <v>91830</v>
+        <v>58043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6238,37 +6231,50 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449620</v>
+        <v>449519</v>
       </c>
       <c r="R44" t="n">
-        <v>6999568</v>
+        <v>6999620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6303,13 +6309,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6318,19 +6328,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Med inslag av björk och sälg.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131223307</v>
       </c>
       <c r="B2" t="n">
-        <v>92535</v>
+        <v>92536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131222541</v>
+        <v>131222821</v>
       </c>
       <c r="B5" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,37 +1122,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Byhögåsen, Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449710</v>
+        <v>449374</v>
       </c>
       <c r="R5" t="n">
-        <v>6999599</v>
+        <v>6999458</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1181,7 +1186,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,12 +1196,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På flera gamla granar.</t>
+          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1225,12 +1230,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1395,10 +1400,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131222821</v>
+        <v>131222541</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1406,42 +1411,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Byhögåsen, Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449374</v>
+        <v>449710</v>
       </c>
       <c r="R7" t="n">
-        <v>6999458</v>
+        <v>6999599</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1687,7 +1687,7 @@
         <v>131231273</v>
       </c>
       <c r="B9" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>131231403</v>
       </c>
       <c r="B10" t="n">
-        <v>92535</v>
+        <v>92536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131231276</v>
+        <v>131231418</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2225,26 +2225,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2252,10 +2257,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449610</v>
+        <v>449617</v>
       </c>
       <c r="R13" t="n">
-        <v>6999650</v>
+        <v>6999646</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2292,7 +2297,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Gott om garnlav på flera granar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2301,7 +2306,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2320,14 +2324,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2345,10 +2344,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131231277</v>
+        <v>131231413</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2356,26 +2355,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2383,10 +2387,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449771</v>
+        <v>449388</v>
       </c>
       <c r="R14" t="n">
-        <v>6999558</v>
+        <v>6999459</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2423,7 +2427,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2432,7 +2436,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2453,12 +2456,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2476,10 +2479,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131231413</v>
+        <v>131231276</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2487,31 +2490,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2519,10 +2517,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449388</v>
+        <v>449610</v>
       </c>
       <c r="R15" t="n">
-        <v>6999459</v>
+        <v>6999650</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2559,7 +2557,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Gott om garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2568,6 +2566,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2588,12 +2587,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2611,10 +2610,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131231418</v>
+        <v>131231277</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2622,31 +2621,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2654,10 +2648,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449617</v>
+        <v>449771</v>
       </c>
       <c r="R16" t="n">
-        <v>6999646</v>
+        <v>6999558</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2694,7 +2688,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2703,6 +2697,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2721,9 +2716,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131231272</v>
+        <v>131231464</v>
       </c>
       <c r="B17" t="n">
-        <v>80351</v>
+        <v>91814</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2752,26 +2752,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2779,10 +2783,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449248</v>
+        <v>449494</v>
       </c>
       <c r="R17" t="n">
-        <v>6999432</v>
+        <v>6999520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2817,11 +2821,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2837,29 +2836,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2877,10 +2866,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131231464</v>
+        <v>131231272</v>
       </c>
       <c r="B18" t="n">
-        <v>91813</v>
+        <v>80352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,30 +2877,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2919,10 +2904,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449494</v>
+        <v>449248</v>
       </c>
       <c r="R18" t="n">
-        <v>6999520</v>
+        <v>6999432</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2957,6 +2942,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2972,19 +2962,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3005,7 +3005,7 @@
         <v>131231279</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>131231426</v>
       </c>
       <c r="B20" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>131231280</v>
       </c>
       <c r="B21" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131231278</v>
       </c>
       <c r="B22" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>131231401</v>
       </c>
       <c r="B24" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131231281</v>
+        <v>131231399</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>91814</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3787,26 +3787,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3814,10 +3818,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449569</v>
+        <v>449456</v>
       </c>
       <c r="R25" t="n">
-        <v>6999561</v>
+        <v>6999489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3852,11 +3856,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3882,14 +3881,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3907,10 +3901,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131231282</v>
+        <v>131231281</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3945,10 +3939,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449559</v>
+        <v>449569</v>
       </c>
       <c r="R26" t="n">
-        <v>6999502</v>
+        <v>6999561</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3981,6 +3975,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4033,10 +4032,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131231399</v>
+        <v>131231282</v>
       </c>
       <c r="B27" t="n">
-        <v>91813</v>
+        <v>79246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4044,30 +4043,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4075,10 +4070,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449456</v>
+        <v>449559</v>
       </c>
       <c r="R27" t="n">
-        <v>6999489</v>
+        <v>6999502</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4138,9 +4133,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131231274</v>
+        <v>131231417</v>
       </c>
       <c r="B28" t="n">
-        <v>91833</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4169,24 +4169,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4196,10 +4201,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449562</v>
+        <v>449423</v>
       </c>
       <c r="R28" t="n">
-        <v>6999557</v>
+        <v>6999465</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4236,7 +4241,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4245,7 +4250,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4264,14 +4268,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4289,10 +4288,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131231417</v>
+        <v>131231274</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>91834</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4300,29 +4299,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4332,10 +4326,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449423</v>
+        <v>449562</v>
       </c>
       <c r="R29" t="n">
-        <v>6999465</v>
+        <v>6999557</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4372,7 +4366,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4381,6 +4375,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4399,9 +4394,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131231275</v>
+        <v>131231416</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4430,26 +4430,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4457,10 +4462,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449233</v>
+        <v>449456</v>
       </c>
       <c r="R30" t="n">
-        <v>6999424</v>
+        <v>6999484</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4495,13 +4500,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4520,14 +4529,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4545,10 +4549,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131231424</v>
+        <v>131231275</v>
       </c>
       <c r="B31" t="n">
-        <v>80350</v>
+        <v>79246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4556,21 +4560,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4583,10 +4587,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449406</v>
+        <v>449233</v>
       </c>
       <c r="R31" t="n">
-        <v>6999460</v>
+        <v>6999424</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4638,22 +4642,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4671,10 +4675,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131231469</v>
+        <v>131231424</v>
       </c>
       <c r="B32" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4709,10 +4713,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449689</v>
+        <v>449406</v>
       </c>
       <c r="R32" t="n">
-        <v>6999668</v>
+        <v>6999460</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4745,11 +4749,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Växer här på sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4802,10 +4801,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131231416</v>
+        <v>131231469</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>80351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4813,31 +4812,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4845,10 +4839,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449456</v>
+        <v>449689</v>
       </c>
       <c r="R33" t="n">
-        <v>6999484</v>
+        <v>6999668</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4885,7 +4879,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Växer här på sälg.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4894,6 +4888,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4904,17 +4899,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131222457</v>
+        <v>131231430</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4943,47 +4943,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åmyren, Åmyren, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449779</v>
+        <v>449758</v>
       </c>
       <c r="R34" t="n">
-        <v>6999560</v>
+        <v>6999616</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5010,24 +5003,14 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5036,6 +5019,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5056,12 +5040,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5079,10 +5063,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131231430</v>
+        <v>131222457</v>
       </c>
       <c r="B35" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5090,40 +5074,47 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449758</v>
+        <v>449779</v>
       </c>
       <c r="R35" t="n">
-        <v>6999616</v>
+        <v>6999560</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5150,14 +5141,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med garnlavsbålar.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5166,7 +5167,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5213,7 +5213,7 @@
         <v>131231425</v>
       </c>
       <c r="B36" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131231414</v>
+        <v>131231402</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>91814</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5347,29 +5347,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5379,10 +5378,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449386</v>
+        <v>449563</v>
       </c>
       <c r="R37" t="n">
-        <v>6999458</v>
+        <v>6999529</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5417,17 +5416,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5466,10 +5461,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131231402</v>
+        <v>131231414</v>
       </c>
       <c r="B38" t="n">
-        <v>91813</v>
+        <v>57884</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5477,28 +5472,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5508,10 +5504,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>449563</v>
+        <v>449386</v>
       </c>
       <c r="R38" t="n">
-        <v>6999529</v>
+        <v>6999458</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5546,13 +5542,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>131231400</v>
       </c>
       <c r="B39" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>131231423</v>
       </c>
       <c r="B40" t="n">
-        <v>79404</v>
+        <v>79405</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>131231429</v>
       </c>
       <c r="B41" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>131231471</v>
       </c>
       <c r="B42" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>131231470</v>
       </c>
       <c r="B43" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -2741,10 +2741,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131231464</v>
+        <v>131231272</v>
       </c>
       <c r="B17" t="n">
-        <v>91814</v>
+        <v>80352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2752,30 +2752,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2783,10 +2779,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449494</v>
+        <v>449248</v>
       </c>
       <c r="R17" t="n">
-        <v>6999520</v>
+        <v>6999432</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2821,6 +2817,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2836,19 +2837,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2866,10 +2877,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131231272</v>
+        <v>131231464</v>
       </c>
       <c r="B18" t="n">
-        <v>80352</v>
+        <v>91814</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2877,26 +2888,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2904,10 +2919,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449248</v>
+        <v>449494</v>
       </c>
       <c r="R18" t="n">
-        <v>6999432</v>
+        <v>6999520</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2942,11 +2957,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2962,29 +2972,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131231401</v>
+        <v>131231281</v>
       </c>
       <c r="B24" t="n">
-        <v>91814</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3662,30 +3662,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3693,10 +3689,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449639</v>
+        <v>449569</v>
       </c>
       <c r="R24" t="n">
-        <v>6999626</v>
+        <v>6999561</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3731,6 +3727,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3756,9 +3757,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3776,10 +3782,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131231399</v>
+        <v>131231282</v>
       </c>
       <c r="B25" t="n">
-        <v>91814</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3787,30 +3793,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3818,10 +3820,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449456</v>
+        <v>449559</v>
       </c>
       <c r="R25" t="n">
-        <v>6999489</v>
+        <v>6999502</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3881,9 +3883,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3901,10 +3908,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131231281</v>
+        <v>131231401</v>
       </c>
       <c r="B26" t="n">
-        <v>79246</v>
+        <v>91814</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3912,26 +3919,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3939,10 +3950,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449569</v>
+        <v>449639</v>
       </c>
       <c r="R26" t="n">
-        <v>6999561</v>
+        <v>6999626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3977,11 +3988,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4007,14 +4013,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4032,10 +4033,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131231282</v>
+        <v>131231399</v>
       </c>
       <c r="B27" t="n">
-        <v>79246</v>
+        <v>91814</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4043,26 +4044,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4070,10 +4075,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449559</v>
+        <v>449456</v>
       </c>
       <c r="R27" t="n">
-        <v>6999502</v>
+        <v>6999489</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4133,14 +4138,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131223307</v>
       </c>
       <c r="B2" t="n">
-        <v>92536</v>
+        <v>92538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131223087</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>131223402</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131222821</v>
+        <v>131223136</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,7 +1142,12 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1151,13 +1156,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449374</v>
+        <v>449315</v>
       </c>
       <c r="R5" t="n">
-        <v>6999458</v>
+        <v>6999445</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1186,7 +1191,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1196,12 +1201,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1253,10 +1258,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131223136</v>
+        <v>131222821</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,12 +1289,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449315</v>
+        <v>449374</v>
       </c>
       <c r="R6" t="n">
-        <v>6999445</v>
+        <v>6999458</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1403,7 +1403,7 @@
         <v>131222541</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131223127</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131231273</v>
+        <v>131231420</v>
       </c>
       <c r="B9" t="n">
-        <v>80351</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1695,28 +1695,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1726,10 +1727,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449640</v>
+        <v>449719</v>
       </c>
       <c r="R9" t="n">
-        <v>6999605</v>
+        <v>6999549</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1766,7 +1767,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1775,7 +1776,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1784,29 +1784,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1824,39 +1814,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131231403</v>
+        <v>131231421</v>
       </c>
       <c r="B10" t="n">
-        <v>92536</v>
+        <v>57886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1866,10 +1857,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449444</v>
+        <v>449687</v>
       </c>
       <c r="R10" t="n">
-        <v>6999489</v>
+        <v>6999537</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1904,13 +1895,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1929,9 +1924,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1949,40 +1949,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131231420</v>
+        <v>131231403</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>92538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1992,10 +1991,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449719</v>
+        <v>449444</v>
       </c>
       <c r="R11" t="n">
-        <v>6999549</v>
+        <v>6999489</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2030,17 +2029,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2079,10 +2074,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131231421</v>
+        <v>131231273</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>80353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2090,29 +2085,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2122,10 +2116,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449687</v>
+        <v>449640</v>
       </c>
       <c r="R12" t="n">
-        <v>6999537</v>
+        <v>6999605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2162,7 +2156,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2171,6 +2165,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2179,24 +2174,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131231418</v>
+        <v>131231413</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2257,10 +2257,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449617</v>
+        <v>449388</v>
       </c>
       <c r="R13" t="n">
-        <v>6999646</v>
+        <v>6999459</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2324,9 +2324,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2344,10 +2349,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131231413</v>
+        <v>131231418</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2377,7 +2382,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2387,10 +2392,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449388</v>
+        <v>449617</v>
       </c>
       <c r="R14" t="n">
-        <v>6999459</v>
+        <v>6999646</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2427,7 +2432,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2454,14 +2459,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131231276</v>
+        <v>131231277</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449610</v>
+        <v>449771</v>
       </c>
       <c r="R15" t="n">
-        <v>6999650</v>
+        <v>6999558</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gott om garnlav på flera granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131231277</v>
+        <v>131231276</v>
       </c>
       <c r="B16" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449771</v>
+        <v>449610</v>
       </c>
       <c r="R16" t="n">
-        <v>6999558</v>
+        <v>6999650</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Gott om garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2741,10 +2741,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131231272</v>
+        <v>131231279</v>
       </c>
       <c r="B17" t="n">
-        <v>80352</v>
+        <v>79248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2752,21 +2752,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449248</v>
+        <v>449722</v>
       </c>
       <c r="R17" t="n">
-        <v>6999432</v>
+        <v>6999656</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2837,29 +2837,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2877,10 +2872,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131231464</v>
+        <v>131231272</v>
       </c>
       <c r="B18" t="n">
-        <v>91814</v>
+        <v>80354</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,30 +2883,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2919,10 +2910,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449494</v>
+        <v>449248</v>
       </c>
       <c r="R18" t="n">
-        <v>6999520</v>
+        <v>6999432</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2957,6 +2948,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2972,19 +2968,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3002,10 +3008,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131231279</v>
+        <v>131231464</v>
       </c>
       <c r="B19" t="n">
-        <v>79246</v>
+        <v>91816</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3013,26 +3019,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3040,10 +3050,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449722</v>
+        <v>449494</v>
       </c>
       <c r="R19" t="n">
-        <v>6999656</v>
+        <v>6999520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3078,11 +3088,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3108,14 +3113,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3136,7 +3136,7 @@
         <v>131231426</v>
       </c>
       <c r="B20" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131231280</v>
+        <v>131231278</v>
       </c>
       <c r="B21" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449639</v>
+        <v>449763</v>
       </c>
       <c r="R21" t="n">
-        <v>6999579</v>
+        <v>6999609</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gott om garnlavsbålar på flera gamla granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3385,10 +3385,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131231278</v>
+        <v>131231280</v>
       </c>
       <c r="B22" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449763</v>
+        <v>449639</v>
       </c>
       <c r="R22" t="n">
-        <v>6999609</v>
+        <v>6999579</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Gott om garnlavsbålar på flera gamla granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3519,7 +3519,7 @@
         <v>131231415</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131231281</v>
+        <v>131231401</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>91816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3662,26 +3662,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3689,10 +3693,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449569</v>
+        <v>449639</v>
       </c>
       <c r="R24" t="n">
-        <v>6999561</v>
+        <v>6999626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3727,11 +3731,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3757,14 +3756,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3782,10 +3776,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131231282</v>
+        <v>131231399</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>91816</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3793,26 +3787,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3820,10 +3818,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449559</v>
+        <v>449456</v>
       </c>
       <c r="R25" t="n">
-        <v>6999502</v>
+        <v>6999489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3883,14 +3881,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3908,10 +3901,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131231401</v>
+        <v>131231282</v>
       </c>
       <c r="B26" t="n">
-        <v>91814</v>
+        <v>79248</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3919,30 +3912,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3950,10 +3939,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449639</v>
+        <v>449559</v>
       </c>
       <c r="R26" t="n">
-        <v>6999626</v>
+        <v>6999502</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4013,9 +4002,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4033,10 +4027,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131231399</v>
+        <v>131231281</v>
       </c>
       <c r="B27" t="n">
-        <v>91814</v>
+        <v>79248</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4044,30 +4038,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4075,10 +4065,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449456</v>
+        <v>449569</v>
       </c>
       <c r="R27" t="n">
-        <v>6999489</v>
+        <v>6999561</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4113,6 +4103,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -4138,9 +4133,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4161,7 +4161,7 @@
         <v>131231417</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         <v>131231274</v>
       </c>
       <c r="B29" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>131231416</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>131231275</v>
       </c>
       <c r="B31" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         <v>131231424</v>
       </c>
       <c r="B32" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>131231469</v>
       </c>
       <c r="B33" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131231430</v>
+        <v>131222457</v>
       </c>
       <c r="B34" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4943,40 +4943,47 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449758</v>
+        <v>449779</v>
       </c>
       <c r="R34" t="n">
-        <v>6999616</v>
+        <v>6999560</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5003,14 +5010,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med garnlavsbålar.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5019,7 +5036,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5040,12 +5056,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5063,10 +5079,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131222457</v>
+        <v>131231430</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5074,47 +5090,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åmyren, Åmyren, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449779</v>
+        <v>449758</v>
       </c>
       <c r="R35" t="n">
-        <v>6999560</v>
+        <v>6999616</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5141,24 +5150,14 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5167,6 +5166,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5213,7 +5213,7 @@
         <v>131231425</v>
       </c>
       <c r="B36" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131231402</v>
+        <v>131231414</v>
       </c>
       <c r="B37" t="n">
-        <v>91814</v>
+        <v>57886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5347,28 +5347,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5378,10 +5379,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449563</v>
+        <v>449386</v>
       </c>
       <c r="R37" t="n">
-        <v>6999529</v>
+        <v>6999458</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5416,13 +5417,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5461,10 +5466,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131231414</v>
+        <v>131231402</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>91816</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5472,29 +5477,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5504,10 +5508,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>449386</v>
+        <v>449563</v>
       </c>
       <c r="R38" t="n">
-        <v>6999458</v>
+        <v>6999529</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5542,17 +5546,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>131231400</v>
       </c>
       <c r="B39" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>131231423</v>
       </c>
       <c r="B40" t="n">
-        <v>79405</v>
+        <v>79407</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131231429</v>
+        <v>131231422</v>
       </c>
       <c r="B41" t="n">
-        <v>79246</v>
+        <v>58045</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5853,37 +5853,50 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449725</v>
+        <v>449519</v>
       </c>
       <c r="R41" t="n">
-        <v>6999697</v>
+        <v>6999620</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5920,7 +5933,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rikligt med garnlavsbålar.</t>
+          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5929,7 +5942,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5938,24 +5950,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Med inslag av björk och sälg.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5973,10 +5970,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131231471</v>
+        <v>131231429</v>
       </c>
       <c r="B42" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6011,10 +6008,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449735</v>
+        <v>449725</v>
       </c>
       <c r="R42" t="n">
-        <v>6999573</v>
+        <v>6999697</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6047,6 +6044,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6099,10 +6101,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131231470</v>
+        <v>131231471</v>
       </c>
       <c r="B43" t="n">
-        <v>91834</v>
+        <v>79248</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6110,26 +6112,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6137,10 +6139,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449620</v>
+        <v>449735</v>
       </c>
       <c r="R43" t="n">
-        <v>6999568</v>
+        <v>6999573</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6200,9 +6202,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6220,10 +6227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131231422</v>
+        <v>131231470</v>
       </c>
       <c r="B44" t="n">
-        <v>58043</v>
+        <v>91836</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6231,50 +6238,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449519</v>
+        <v>449620</v>
       </c>
       <c r="R44" t="n">
-        <v>6999620</v>
+        <v>6999568</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6309,17 +6303,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6328,9 +6318,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Med inslag av björk och sälg.</t>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131223307</v>
       </c>
       <c r="B2" t="n">
-        <v>92538</v>
+        <v>92539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131223087</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>131223402</v>
       </c>
       <c r="B4" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>131223136</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>131222821</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>131222541</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131223127</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>131231420</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>131231421</v>
       </c>
       <c r="B10" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1949,39 +1949,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131231403</v>
+        <v>131231273</v>
       </c>
       <c r="B11" t="n">
-        <v>92538</v>
+        <v>80354</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449444</v>
+        <v>449640</v>
       </c>
       <c r="R11" t="n">
-        <v>6999489</v>
+        <v>6999605</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2029,6 +2029,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -2044,19 +2049,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2074,39 +2089,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131231273</v>
+        <v>131231403</v>
       </c>
       <c r="B12" t="n">
-        <v>80353</v>
+        <v>92539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2116,10 +2131,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449640</v>
+        <v>449444</v>
       </c>
       <c r="R12" t="n">
-        <v>6999605</v>
+        <v>6999489</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2154,11 +2169,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2174,29 +2184,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2217,7 +2217,7 @@
         <v>131231413</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>131231418</v>
       </c>
       <c r="B14" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2479,10 +2479,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131231277</v>
+        <v>131231276</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449771</v>
+        <v>449610</v>
       </c>
       <c r="R15" t="n">
-        <v>6999558</v>
+        <v>6999650</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Gott om garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131231276</v>
+        <v>131231277</v>
       </c>
       <c r="B16" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449610</v>
+        <v>449771</v>
       </c>
       <c r="R16" t="n">
-        <v>6999650</v>
+        <v>6999558</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gott om garnlav på flera granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2741,10 +2741,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131231279</v>
+        <v>131231272</v>
       </c>
       <c r="B17" t="n">
-        <v>79248</v>
+        <v>80355</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2752,21 +2752,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449722</v>
+        <v>449248</v>
       </c>
       <c r="R17" t="n">
-        <v>6999656</v>
+        <v>6999432</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2837,24 +2837,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2872,10 +2877,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131231272</v>
+        <v>131231464</v>
       </c>
       <c r="B18" t="n">
-        <v>80354</v>
+        <v>91817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2883,26 +2888,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2910,10 +2919,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449248</v>
+        <v>449494</v>
       </c>
       <c r="R18" t="n">
-        <v>6999432</v>
+        <v>6999520</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2948,11 +2957,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2968,29 +2972,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3008,10 +3002,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131231464</v>
+        <v>131231279</v>
       </c>
       <c r="B19" t="n">
-        <v>91816</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3019,30 +3013,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3050,10 +3040,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449494</v>
+        <v>449722</v>
       </c>
       <c r="R19" t="n">
-        <v>6999520</v>
+        <v>6999656</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3088,6 +3078,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3113,9 +3108,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3136,7 +3136,7 @@
         <v>131231426</v>
       </c>
       <c r="B20" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3254,10 +3254,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131231278</v>
+        <v>131231280</v>
       </c>
       <c r="B21" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3292,10 +3292,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449763</v>
+        <v>449639</v>
       </c>
       <c r="R21" t="n">
-        <v>6999609</v>
+        <v>6999579</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Gott om garnlavsbålar på flera gamla granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3385,10 +3385,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131231280</v>
+        <v>131231278</v>
       </c>
       <c r="B22" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3423,10 +3423,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449639</v>
+        <v>449763</v>
       </c>
       <c r="R22" t="n">
-        <v>6999579</v>
+        <v>6999609</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gott om garnlavsbålar på flera gamla granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3519,7 +3519,7 @@
         <v>131231415</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>131231401</v>
       </c>
       <c r="B24" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>131231399</v>
       </c>
       <c r="B25" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3901,10 +3901,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131231282</v>
+        <v>131231281</v>
       </c>
       <c r="B26" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449559</v>
+        <v>449569</v>
       </c>
       <c r="R26" t="n">
-        <v>6999502</v>
+        <v>6999561</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3975,6 +3975,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4027,10 +4032,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131231281</v>
+        <v>131231282</v>
       </c>
       <c r="B27" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4065,10 +4070,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449569</v>
+        <v>449559</v>
       </c>
       <c r="R27" t="n">
-        <v>6999561</v>
+        <v>6999502</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4101,11 +4106,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131231417</v>
+        <v>131231274</v>
       </c>
       <c r="B28" t="n">
-        <v>57886</v>
+        <v>91837</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4169,29 +4169,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4201,10 +4196,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449423</v>
+        <v>449562</v>
       </c>
       <c r="R28" t="n">
-        <v>6999465</v>
+        <v>6999557</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4241,7 +4236,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4250,6 +4245,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4268,9 +4264,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4288,10 +4289,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131231274</v>
+        <v>131231417</v>
       </c>
       <c r="B29" t="n">
-        <v>91836</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4299,24 +4300,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4326,10 +4332,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449562</v>
+        <v>449423</v>
       </c>
       <c r="R29" t="n">
-        <v>6999557</v>
+        <v>6999465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4366,7 +4372,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4375,7 +4381,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4394,14 +4399,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131231416</v>
+        <v>131231424</v>
       </c>
       <c r="B30" t="n">
-        <v>57886</v>
+        <v>80354</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4430,31 +4430,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4462,10 +4457,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449456</v>
+        <v>449406</v>
       </c>
       <c r="R30" t="n">
-        <v>6999484</v>
+        <v>6999460</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4500,17 +4495,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4521,17 +4512,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4549,10 +4545,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131231275</v>
+        <v>131231469</v>
       </c>
       <c r="B31" t="n">
-        <v>79248</v>
+        <v>80354</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4560,21 +4556,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4587,10 +4583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449233</v>
+        <v>449689</v>
       </c>
       <c r="R31" t="n">
-        <v>6999424</v>
+        <v>6999668</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4625,6 +4621,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växer här på sälg.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4642,22 +4643,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4675,10 +4676,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131231424</v>
+        <v>131231416</v>
       </c>
       <c r="B32" t="n">
-        <v>80353</v>
+        <v>57887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4686,26 +4687,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4713,10 +4719,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449406</v>
+        <v>449456</v>
       </c>
       <c r="R32" t="n">
-        <v>6999460</v>
+        <v>6999484</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4751,13 +4757,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4768,22 +4778,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4801,10 +4806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131231469</v>
+        <v>131231275</v>
       </c>
       <c r="B33" t="n">
-        <v>80353</v>
+        <v>79249</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4812,21 +4817,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4839,10 +4844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449689</v>
+        <v>449233</v>
       </c>
       <c r="R33" t="n">
-        <v>6999668</v>
+        <v>6999424</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4877,11 +4882,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Växer här på sälg.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4899,22 +4899,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131222457</v>
+        <v>131231430</v>
       </c>
       <c r="B34" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4943,47 +4943,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åmyren, Åmyren, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449779</v>
+        <v>449758</v>
       </c>
       <c r="R34" t="n">
-        <v>6999560</v>
+        <v>6999616</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5010,24 +5003,14 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5036,6 +5019,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5056,12 +5040,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5079,10 +5063,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131231430</v>
+        <v>131222457</v>
       </c>
       <c r="B35" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5090,40 +5074,47 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449758</v>
+        <v>449779</v>
       </c>
       <c r="R35" t="n">
-        <v>6999616</v>
+        <v>6999560</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5150,14 +5141,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med garnlavsbålar.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5166,7 +5167,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5213,7 +5213,7 @@
         <v>131231425</v>
       </c>
       <c r="B36" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131231414</v>
+        <v>131231402</v>
       </c>
       <c r="B37" t="n">
-        <v>57886</v>
+        <v>91817</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5347,29 +5347,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5379,10 +5378,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449386</v>
+        <v>449563</v>
       </c>
       <c r="R37" t="n">
-        <v>6999458</v>
+        <v>6999529</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5417,17 +5416,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5466,10 +5461,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131231402</v>
+        <v>131231414</v>
       </c>
       <c r="B38" t="n">
-        <v>91816</v>
+        <v>57887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5477,28 +5472,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5508,10 +5504,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>449563</v>
+        <v>449386</v>
       </c>
       <c r="R38" t="n">
-        <v>6999529</v>
+        <v>6999458</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5546,13 +5542,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>131231400</v>
       </c>
       <c r="B39" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>131231423</v>
       </c>
       <c r="B40" t="n">
-        <v>79407</v>
+        <v>79408</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131231422</v>
+        <v>131231429</v>
       </c>
       <c r="B41" t="n">
-        <v>58045</v>
+        <v>79249</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5853,50 +5853,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449519</v>
+        <v>449725</v>
       </c>
       <c r="R41" t="n">
-        <v>6999620</v>
+        <v>6999697</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5933,7 +5920,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5942,6 +5929,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5950,9 +5938,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>Med inslag av björk och sälg.</t>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5970,10 +5973,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131231429</v>
+        <v>131231471</v>
       </c>
       <c r="B42" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6008,10 +6011,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449725</v>
+        <v>449735</v>
       </c>
       <c r="R42" t="n">
-        <v>6999697</v>
+        <v>6999573</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6044,11 +6047,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6101,10 +6099,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131231471</v>
+        <v>131231470</v>
       </c>
       <c r="B43" t="n">
-        <v>79248</v>
+        <v>91837</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6112,26 +6110,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6139,10 +6137,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449735</v>
+        <v>449620</v>
       </c>
       <c r="R43" t="n">
-        <v>6999573</v>
+        <v>6999568</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6202,14 +6200,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6227,10 +6220,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131231470</v>
+        <v>131231422</v>
       </c>
       <c r="B44" t="n">
-        <v>91836</v>
+        <v>58046</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6238,37 +6231,50 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449620</v>
+        <v>449519</v>
       </c>
       <c r="R44" t="n">
-        <v>6999568</v>
+        <v>6999620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6303,13 +6309,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6318,19 +6328,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Med inslag av björk och sälg.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -1111,10 +1111,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131223136</v>
+        <v>131222541</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,47 +1122,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Byhögåsen, Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449315</v>
+        <v>449710</v>
       </c>
       <c r="R5" t="n">
-        <v>6999445</v>
+        <v>6999599</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1191,7 +1181,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1201,12 +1191,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1235,12 +1225,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1258,7 +1248,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131222821</v>
+        <v>131223136</v>
       </c>
       <c r="B6" t="n">
         <v>57887</v>
@@ -1289,7 +1279,12 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1298,13 +1293,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449374</v>
+        <v>449315</v>
       </c>
       <c r="R6" t="n">
-        <v>6999458</v>
+        <v>6999445</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1333,7 +1328,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1343,12 +1338,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1400,10 +1395,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131222541</v>
+        <v>131222821</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1411,37 +1406,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Byhögåsen, Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449710</v>
+        <v>449374</v>
       </c>
       <c r="R7" t="n">
-        <v>6999599</v>
+        <v>6999458</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På flera gamla granar.</t>
+          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1684,40 +1684,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131231420</v>
+        <v>131231403</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>92539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1727,10 +1726,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449719</v>
+        <v>449444</v>
       </c>
       <c r="R9" t="n">
-        <v>6999549</v>
+        <v>6999489</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1765,17 +1764,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1814,10 +1809,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131231421</v>
+        <v>131231273</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1825,29 +1820,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1857,10 +1851,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449687</v>
+        <v>449640</v>
       </c>
       <c r="R10" t="n">
-        <v>6999537</v>
+        <v>6999605</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1897,7 +1891,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1906,6 +1900,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1914,24 +1909,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131231273</v>
+        <v>131231420</v>
       </c>
       <c r="B11" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1960,28 +1960,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1991,10 +1992,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449640</v>
+        <v>449719</v>
       </c>
       <c r="R11" t="n">
-        <v>6999605</v>
+        <v>6999549</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2031,7 +2032,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2040,7 +2041,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2049,29 +2049,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2089,39 +2079,40 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131231403</v>
+        <v>131231421</v>
       </c>
       <c r="B12" t="n">
-        <v>92539</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2131,10 +2122,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449444</v>
+        <v>449687</v>
       </c>
       <c r="R12" t="n">
-        <v>6999489</v>
+        <v>6999537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2169,13 +2160,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2194,9 +2189,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131231413</v>
+        <v>131231276</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2225,31 +2225,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2257,10 +2252,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449388</v>
+        <v>449610</v>
       </c>
       <c r="R13" t="n">
-        <v>6999459</v>
+        <v>6999650</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2297,7 +2292,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Gott om garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2306,6 +2301,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2326,12 +2322,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2349,10 +2345,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131231418</v>
+        <v>131231277</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2360,31 +2356,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2392,10 +2383,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449617</v>
+        <v>449771</v>
       </c>
       <c r="R14" t="n">
-        <v>6999646</v>
+        <v>6999558</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2432,7 +2423,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2441,6 +2432,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2459,9 +2451,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2479,10 +2476,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131231276</v>
+        <v>131231413</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2490,26 +2487,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2517,10 +2519,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449610</v>
+        <v>449388</v>
       </c>
       <c r="R15" t="n">
-        <v>6999650</v>
+        <v>6999459</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2557,7 +2559,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gott om garnlav på flera granar.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2566,7 +2568,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2587,12 +2588,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2610,10 +2611,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131231277</v>
+        <v>131231418</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2621,26 +2622,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2648,10 +2654,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449771</v>
+        <v>449617</v>
       </c>
       <c r="R16" t="n">
-        <v>6999558</v>
+        <v>6999646</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2688,7 +2694,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2697,7 +2703,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2716,14 +2721,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131231272</v>
+        <v>131231464</v>
       </c>
       <c r="B17" t="n">
-        <v>80355</v>
+        <v>91817</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2752,26 +2752,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2779,10 +2783,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449248</v>
+        <v>449494</v>
       </c>
       <c r="R17" t="n">
-        <v>6999432</v>
+        <v>6999520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2817,11 +2821,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2837,29 +2836,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2877,10 +2866,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131231464</v>
+        <v>131231272</v>
       </c>
       <c r="B18" t="n">
-        <v>91817</v>
+        <v>80355</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,30 +2877,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2919,10 +2904,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449494</v>
+        <v>449248</v>
       </c>
       <c r="R18" t="n">
-        <v>6999520</v>
+        <v>6999432</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2957,6 +2942,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2972,19 +2962,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131231274</v>
+        <v>131231417</v>
       </c>
       <c r="B28" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4169,24 +4169,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4196,10 +4201,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449562</v>
+        <v>449423</v>
       </c>
       <c r="R28" t="n">
-        <v>6999557</v>
+        <v>6999465</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4236,7 +4241,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4245,7 +4250,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4264,14 +4268,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4289,10 +4288,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131231417</v>
+        <v>131231274</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4300,29 +4299,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4332,10 +4326,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449423</v>
+        <v>449562</v>
       </c>
       <c r="R29" t="n">
-        <v>6999465</v>
+        <v>6999557</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4372,7 +4366,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4381,6 +4375,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4399,9 +4394,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4545,10 +4545,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131231469</v>
+        <v>131231275</v>
       </c>
       <c r="B31" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4556,21 +4556,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449689</v>
+        <v>449233</v>
       </c>
       <c r="R31" t="n">
-        <v>6999668</v>
+        <v>6999424</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4621,11 +4621,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Växer här på sälg.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4643,22 +4638,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4676,10 +4671,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131231416</v>
+        <v>131231469</v>
       </c>
       <c r="B32" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4687,31 +4682,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4719,10 +4709,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449456</v>
+        <v>449689</v>
       </c>
       <c r="R32" t="n">
-        <v>6999484</v>
+        <v>6999668</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4759,7 +4749,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Växer här på sälg.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4768,6 +4758,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4778,17 +4769,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4806,10 +4802,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131231275</v>
+        <v>131231416</v>
       </c>
       <c r="B33" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4817,26 +4813,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4844,10 +4845,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449233</v>
+        <v>449456</v>
       </c>
       <c r="R33" t="n">
-        <v>6999424</v>
+        <v>6999484</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4882,13 +4883,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4907,14 +4912,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131231429</v>
+        <v>131231470</v>
       </c>
       <c r="B41" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5853,26 +5853,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5880,10 +5880,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449725</v>
+        <v>449620</v>
       </c>
       <c r="R41" t="n">
-        <v>6999697</v>
+        <v>6999568</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5918,11 +5918,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlavsbålar.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5948,14 +5943,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5973,10 +5963,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131231471</v>
+        <v>131231422</v>
       </c>
       <c r="B42" t="n">
-        <v>79249</v>
+        <v>58046</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5984,37 +5974,50 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449735</v>
+        <v>449519</v>
       </c>
       <c r="R42" t="n">
-        <v>6999573</v>
+        <v>6999620</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6049,13 +6052,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6064,24 +6071,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Med inslag av björk och sälg.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6099,10 +6091,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131231470</v>
+        <v>131231429</v>
       </c>
       <c r="B43" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6110,26 +6102,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6137,10 +6129,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449620</v>
+        <v>449725</v>
       </c>
       <c r="R43" t="n">
-        <v>6999568</v>
+        <v>6999697</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6175,6 +6167,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlavsbålar.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6200,9 +6197,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6220,10 +6222,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131231422</v>
+        <v>131231471</v>
       </c>
       <c r="B44" t="n">
-        <v>58046</v>
+        <v>79249</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6231,50 +6233,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449519</v>
+        <v>449735</v>
       </c>
       <c r="R44" t="n">
-        <v>6999620</v>
+        <v>6999573</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6309,17 +6298,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6328,9 +6313,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Med inslag av björk och sälg.</t>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -1248,7 +1248,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131223136</v>
+        <v>131222821</v>
       </c>
       <c r="B6" t="n">
         <v>57887</v>
@@ -1279,12 +1279,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1293,13 +1288,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449315</v>
+        <v>449374</v>
       </c>
       <c r="R6" t="n">
-        <v>6999445</v>
+        <v>6999458</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1328,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1338,12 +1333,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1395,7 +1390,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131222821</v>
+        <v>131223136</v>
       </c>
       <c r="B7" t="n">
         <v>57887</v>
@@ -1426,7 +1421,12 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449374</v>
+        <v>449315</v>
       </c>
       <c r="R7" t="n">
-        <v>6999458</v>
+        <v>6999445</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1684,39 +1684,40 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131231403</v>
+        <v>131231420</v>
       </c>
       <c r="B9" t="n">
-        <v>92539</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1726,10 +1727,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449444</v>
+        <v>449719</v>
       </c>
       <c r="R9" t="n">
-        <v>6999489</v>
+        <v>6999549</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1764,13 +1765,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1809,10 +1814,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131231273</v>
+        <v>131231421</v>
       </c>
       <c r="B10" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1820,28 +1825,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1851,10 +1857,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449640</v>
+        <v>449687</v>
       </c>
       <c r="R10" t="n">
-        <v>6999605</v>
+        <v>6999537</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1891,7 +1897,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1900,7 +1906,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1909,29 +1914,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1949,40 +1949,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131231420</v>
+        <v>131231403</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>92539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1992,10 +1991,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449719</v>
+        <v>449444</v>
       </c>
       <c r="R11" t="n">
-        <v>6999549</v>
+        <v>6999489</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2030,17 +2029,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2079,10 +2074,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131231421</v>
+        <v>131231273</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2090,29 +2085,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2122,10 +2116,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449687</v>
+        <v>449640</v>
       </c>
       <c r="R12" t="n">
-        <v>6999537</v>
+        <v>6999605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2162,7 +2156,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2171,6 +2165,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2179,24 +2174,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131231417</v>
+        <v>131231274</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4169,29 +4169,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4201,10 +4196,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449423</v>
+        <v>449562</v>
       </c>
       <c r="R28" t="n">
-        <v>6999465</v>
+        <v>6999557</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4241,7 +4236,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4250,6 +4245,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4268,9 +4264,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4288,10 +4289,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131231274</v>
+        <v>131231417</v>
       </c>
       <c r="B29" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4299,24 +4300,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4326,10 +4332,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449562</v>
+        <v>449423</v>
       </c>
       <c r="R29" t="n">
-        <v>6999557</v>
+        <v>6999465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4366,7 +4372,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4375,7 +4381,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4394,14 +4399,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4545,10 +4545,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131231275</v>
+        <v>131231469</v>
       </c>
       <c r="B31" t="n">
-        <v>79249</v>
+        <v>80354</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4556,21 +4556,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449233</v>
+        <v>449689</v>
       </c>
       <c r="R31" t="n">
-        <v>6999424</v>
+        <v>6999668</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4621,6 +4621,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växer här på sälg.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4638,22 +4643,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4671,10 +4676,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131231469</v>
+        <v>131231275</v>
       </c>
       <c r="B32" t="n">
-        <v>80354</v>
+        <v>79249</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4682,21 +4687,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4709,10 +4714,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449689</v>
+        <v>449233</v>
       </c>
       <c r="R32" t="n">
-        <v>6999668</v>
+        <v>6999424</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4747,11 +4752,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Växer här på sälg.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4769,22 +4769,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131231430</v>
+        <v>131222457</v>
       </c>
       <c r="B34" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4943,40 +4943,47 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449758</v>
+        <v>449779</v>
       </c>
       <c r="R34" t="n">
-        <v>6999616</v>
+        <v>6999560</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5003,14 +5010,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med garnlavsbålar.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5019,7 +5036,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5040,12 +5056,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5063,10 +5079,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131222457</v>
+        <v>131231430</v>
       </c>
       <c r="B35" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5074,47 +5090,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åmyren, Åmyren, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449779</v>
+        <v>449758</v>
       </c>
       <c r="R35" t="n">
-        <v>6999560</v>
+        <v>6999616</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5141,24 +5150,14 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5167,6 +5166,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131231470</v>
+        <v>131231429</v>
       </c>
       <c r="B41" t="n">
-        <v>91837</v>
+        <v>79249</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5853,26 +5853,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5880,10 +5880,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449620</v>
+        <v>449725</v>
       </c>
       <c r="R41" t="n">
-        <v>6999568</v>
+        <v>6999697</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5918,6 +5918,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlavsbålar.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5943,9 +5948,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5963,10 +5973,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131231422</v>
+        <v>131231471</v>
       </c>
       <c r="B42" t="n">
-        <v>58046</v>
+        <v>79249</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5974,50 +5984,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449519</v>
+        <v>449735</v>
       </c>
       <c r="R42" t="n">
-        <v>6999620</v>
+        <v>6999573</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6052,17 +6049,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6071,9 +6064,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Med inslag av björk och sälg.</t>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6091,10 +6099,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131231429</v>
+        <v>131231470</v>
       </c>
       <c r="B43" t="n">
-        <v>79249</v>
+        <v>91837</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6102,26 +6110,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6129,10 +6137,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449725</v>
+        <v>449620</v>
       </c>
       <c r="R43" t="n">
-        <v>6999697</v>
+        <v>6999568</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6167,11 +6175,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlavsbålar.</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -6197,14 +6200,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6222,10 +6220,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131231471</v>
+        <v>131231422</v>
       </c>
       <c r="B44" t="n">
-        <v>79249</v>
+        <v>58046</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6233,37 +6231,50 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449735</v>
+        <v>449519</v>
       </c>
       <c r="R44" t="n">
-        <v>6999573</v>
+        <v>6999620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6298,13 +6309,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6313,24 +6328,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Med inslag av björk och sälg.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131223307</v>
       </c>
       <c r="B2" t="n">
-        <v>92539</v>
+        <v>92540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131223087</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>131223402</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>131222541</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>131222821</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>131223136</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131223127</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,40 +1684,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131231420</v>
+        <v>131231403</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>92540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1727,10 +1726,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449719</v>
+        <v>449444</v>
       </c>
       <c r="R9" t="n">
-        <v>6999549</v>
+        <v>6999489</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1765,17 +1764,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1814,10 +1809,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131231421</v>
+        <v>131231273</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>80355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1825,29 +1820,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1857,10 +1851,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449687</v>
+        <v>449640</v>
       </c>
       <c r="R10" t="n">
-        <v>6999537</v>
+        <v>6999605</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1897,7 +1891,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1906,6 +1900,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1914,24 +1909,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1949,39 +1949,40 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131231403</v>
+        <v>131231420</v>
       </c>
       <c r="B11" t="n">
-        <v>92539</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1991,10 +1992,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449444</v>
+        <v>449719</v>
       </c>
       <c r="R11" t="n">
-        <v>6999489</v>
+        <v>6999549</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2029,13 +2030,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2074,10 +2079,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131231273</v>
+        <v>131231421</v>
       </c>
       <c r="B12" t="n">
-        <v>80354</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2085,28 +2090,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2116,10 +2122,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449640</v>
+        <v>449687</v>
       </c>
       <c r="R12" t="n">
-        <v>6999605</v>
+        <v>6999537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2156,7 +2162,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2165,7 +2171,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2174,29 +2179,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2217,7 +2217,7 @@
         <v>131231276</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>131231277</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         <v>131231413</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>131231418</v>
       </c>
       <c r="B16" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>131231464</v>
       </c>
       <c r="B17" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         <v>131231272</v>
       </c>
       <c r="B18" t="n">
-        <v>80355</v>
+        <v>80356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>131231279</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>131231426</v>
       </c>
       <c r="B20" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>131231280</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131231278</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>131231415</v>
       </c>
       <c r="B23" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131231401</v>
+        <v>131231399</v>
       </c>
       <c r="B24" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3693,10 +3693,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449639</v>
+        <v>449456</v>
       </c>
       <c r="R24" t="n">
-        <v>6999626</v>
+        <v>6999489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131231399</v>
+        <v>131231401</v>
       </c>
       <c r="B25" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3818,10 +3818,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449456</v>
+        <v>449639</v>
       </c>
       <c r="R25" t="n">
-        <v>6999489</v>
+        <v>6999626</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3904,7 +3904,7 @@
         <v>131231281</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>131231282</v>
       </c>
       <c r="B27" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131231274</v>
+        <v>131231417</v>
       </c>
       <c r="B28" t="n">
-        <v>91837</v>
+        <v>57888</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4169,24 +4169,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4196,10 +4201,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449562</v>
+        <v>449423</v>
       </c>
       <c r="R28" t="n">
-        <v>6999557</v>
+        <v>6999465</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4236,7 +4241,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4245,7 +4250,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4264,14 +4268,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4289,10 +4288,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131231417</v>
+        <v>131231274</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4300,29 +4299,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4332,10 +4326,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449423</v>
+        <v>449562</v>
       </c>
       <c r="R29" t="n">
-        <v>6999465</v>
+        <v>6999557</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4372,7 +4366,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4381,6 +4375,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4399,9 +4394,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131231424</v>
+        <v>131231275</v>
       </c>
       <c r="B30" t="n">
-        <v>80354</v>
+        <v>79250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449406</v>
+        <v>449233</v>
       </c>
       <c r="R30" t="n">
-        <v>6999460</v>
+        <v>6999424</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4512,22 +4512,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4545,10 +4545,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131231469</v>
+        <v>131231424</v>
       </c>
       <c r="B31" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449689</v>
+        <v>449406</v>
       </c>
       <c r="R31" t="n">
-        <v>6999668</v>
+        <v>6999460</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4619,11 +4619,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Växer här på sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4676,10 +4671,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131231275</v>
+        <v>131231469</v>
       </c>
       <c r="B32" t="n">
-        <v>79249</v>
+        <v>80355</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4687,21 +4682,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4714,10 +4709,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449233</v>
+        <v>449689</v>
       </c>
       <c r="R32" t="n">
-        <v>6999424</v>
+        <v>6999668</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4752,6 +4747,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Växer här på sälg.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4769,22 +4769,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4805,7 +4805,7 @@
         <v>131231416</v>
       </c>
       <c r="B33" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131222457</v>
+        <v>131231430</v>
       </c>
       <c r="B34" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4943,47 +4943,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åmyren, Åmyren, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449779</v>
+        <v>449758</v>
       </c>
       <c r="R34" t="n">
-        <v>6999560</v>
+        <v>6999616</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5010,24 +5003,14 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5036,6 +5019,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5056,12 +5040,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5079,10 +5063,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131231430</v>
+        <v>131222457</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5090,40 +5074,47 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449758</v>
+        <v>449779</v>
       </c>
       <c r="R35" t="n">
-        <v>6999616</v>
+        <v>6999560</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5150,14 +5141,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med garnlavsbålar.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5166,7 +5167,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5213,7 +5213,7 @@
         <v>131231425</v>
       </c>
       <c r="B36" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>131231402</v>
       </c>
       <c r="B37" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>131231414</v>
       </c>
       <c r="B38" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>131231400</v>
       </c>
       <c r="B39" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>131231423</v>
       </c>
       <c r="B40" t="n">
-        <v>79408</v>
+        <v>79409</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>131231429</v>
       </c>
       <c r="B41" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5973,10 +5973,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131231471</v>
+        <v>131231470</v>
       </c>
       <c r="B42" t="n">
-        <v>79249</v>
+        <v>91838</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5984,26 +5984,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449735</v>
+        <v>449620</v>
       </c>
       <c r="R42" t="n">
-        <v>6999573</v>
+        <v>6999568</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6074,14 +6074,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6099,10 +6094,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131231470</v>
+        <v>131231471</v>
       </c>
       <c r="B43" t="n">
-        <v>91837</v>
+        <v>79250</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6110,26 +6105,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6137,10 +6132,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449620</v>
+        <v>449735</v>
       </c>
       <c r="R43" t="n">
-        <v>6999568</v>
+        <v>6999573</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6200,9 +6195,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6223,7 +6223,7 @@
         <v>131231422</v>
       </c>
       <c r="B44" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -1248,7 +1248,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131222821</v>
+        <v>131223136</v>
       </c>
       <c r="B6" t="n">
         <v>57888</v>
@@ -1279,7 +1279,12 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1288,13 +1293,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449374</v>
+        <v>449315</v>
       </c>
       <c r="R6" t="n">
-        <v>6999458</v>
+        <v>6999445</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1323,7 +1328,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1333,12 +1338,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1390,7 +1395,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131223136</v>
+        <v>131222821</v>
       </c>
       <c r="B7" t="n">
         <v>57888</v>
@@ -1421,12 +1426,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449315</v>
+        <v>449374</v>
       </c>
       <c r="R7" t="n">
-        <v>6999445</v>
+        <v>6999458</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1684,39 +1684,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131231403</v>
+        <v>131231273</v>
       </c>
       <c r="B9" t="n">
-        <v>92540</v>
+        <v>80355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449444</v>
+        <v>449640</v>
       </c>
       <c r="R9" t="n">
-        <v>6999489</v>
+        <v>6999605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1764,6 +1764,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1779,19 +1784,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1809,39 +1824,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131231273</v>
+        <v>131231403</v>
       </c>
       <c r="B10" t="n">
-        <v>80355</v>
+        <v>92540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1851,10 +1866,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449640</v>
+        <v>449444</v>
       </c>
       <c r="R10" t="n">
-        <v>6999605</v>
+        <v>6999489</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1889,11 +1904,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1909,29 +1919,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131231277</v>
+        <v>131231413</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2356,26 +2356,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2383,10 +2388,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449771</v>
+        <v>449388</v>
       </c>
       <c r="R14" t="n">
-        <v>6999558</v>
+        <v>6999459</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2423,7 +2428,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2432,7 +2437,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2453,12 +2457,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2476,7 +2480,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131231413</v>
+        <v>131231418</v>
       </c>
       <c r="B15" t="n">
         <v>57888</v>
@@ -2509,7 +2513,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2519,10 +2523,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449388</v>
+        <v>449617</v>
       </c>
       <c r="R15" t="n">
-        <v>6999459</v>
+        <v>6999646</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2559,7 +2563,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2586,14 +2590,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2611,10 +2610,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131231418</v>
+        <v>131231277</v>
       </c>
       <c r="B16" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2622,31 +2621,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2654,10 +2648,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449617</v>
+        <v>449771</v>
       </c>
       <c r="R16" t="n">
-        <v>6999646</v>
+        <v>6999558</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2694,7 +2688,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2703,6 +2697,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2721,9 +2716,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2741,10 +2741,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131231464</v>
+        <v>131231272</v>
       </c>
       <c r="B17" t="n">
-        <v>91818</v>
+        <v>80356</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2752,30 +2752,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2783,10 +2779,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449494</v>
+        <v>449248</v>
       </c>
       <c r="R17" t="n">
-        <v>6999520</v>
+        <v>6999432</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2821,6 +2817,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2836,19 +2837,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2866,10 +2877,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131231272</v>
+        <v>131231464</v>
       </c>
       <c r="B18" t="n">
-        <v>80356</v>
+        <v>91818</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2877,26 +2888,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2904,10 +2919,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449248</v>
+        <v>449494</v>
       </c>
       <c r="R18" t="n">
-        <v>6999432</v>
+        <v>6999520</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2942,11 +2957,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2962,29 +2972,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131231426</v>
+        <v>131231280</v>
       </c>
       <c r="B20" t="n">
-        <v>91838</v>
+        <v>79250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3144,26 +3144,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449572</v>
+        <v>449639</v>
       </c>
       <c r="R20" t="n">
-        <v>6999535</v>
+        <v>6999579</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3209,6 +3209,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gott om garnlavsbålar på flera gamla granar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3234,9 +3239,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3254,7 +3264,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131231280</v>
+        <v>131231278</v>
       </c>
       <c r="B21" t="n">
         <v>79250</v>
@@ -3292,10 +3302,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449639</v>
+        <v>449763</v>
       </c>
       <c r="R21" t="n">
-        <v>6999579</v>
+        <v>6999609</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3332,7 +3342,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gott om garnlavsbålar på flera gamla granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3385,10 +3395,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131231278</v>
+        <v>131231426</v>
       </c>
       <c r="B22" t="n">
-        <v>79250</v>
+        <v>91838</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3396,26 +3406,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3423,10 +3433,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449763</v>
+        <v>449572</v>
       </c>
       <c r="R22" t="n">
-        <v>6999609</v>
+        <v>6999535</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3461,11 +3471,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3491,14 +3496,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131231399</v>
+        <v>131231281</v>
       </c>
       <c r="B24" t="n">
-        <v>91818</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3662,30 +3662,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3693,10 +3689,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449456</v>
+        <v>449569</v>
       </c>
       <c r="R24" t="n">
-        <v>6999489</v>
+        <v>6999561</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3731,6 +3727,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3756,9 +3757,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3776,10 +3782,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131231401</v>
+        <v>131231282</v>
       </c>
       <c r="B25" t="n">
-        <v>91818</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3787,30 +3793,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3818,10 +3820,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449639</v>
+        <v>449559</v>
       </c>
       <c r="R25" t="n">
-        <v>6999626</v>
+        <v>6999502</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3881,9 +3883,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3901,10 +3908,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131231281</v>
+        <v>131231401</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>91818</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3912,26 +3919,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3939,10 +3950,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449569</v>
+        <v>449639</v>
       </c>
       <c r="R26" t="n">
-        <v>6999561</v>
+        <v>6999626</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3977,11 +3988,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4007,14 +4013,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4032,10 +4033,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131231282</v>
+        <v>131231399</v>
       </c>
       <c r="B27" t="n">
-        <v>79250</v>
+        <v>91818</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4043,26 +4044,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4070,10 +4075,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449559</v>
+        <v>449456</v>
       </c>
       <c r="R27" t="n">
-        <v>6999502</v>
+        <v>6999489</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4133,14 +4138,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131231417</v>
+        <v>131231274</v>
       </c>
       <c r="B28" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4169,29 +4169,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4201,10 +4196,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449423</v>
+        <v>449562</v>
       </c>
       <c r="R28" t="n">
-        <v>6999465</v>
+        <v>6999557</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4241,7 +4236,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4250,6 +4245,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4268,9 +4264,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4288,10 +4289,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131231274</v>
+        <v>131231417</v>
       </c>
       <c r="B29" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4299,24 +4300,29 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4326,10 +4332,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449562</v>
+        <v>449423</v>
       </c>
       <c r="R29" t="n">
-        <v>6999557</v>
+        <v>6999465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4366,7 +4372,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4375,7 +4381,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4394,14 +4399,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131231275</v>
+        <v>131231424</v>
       </c>
       <c r="B30" t="n">
-        <v>79250</v>
+        <v>80355</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449233</v>
+        <v>449406</v>
       </c>
       <c r="R30" t="n">
-        <v>6999424</v>
+        <v>6999460</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4512,22 +4512,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4545,7 +4545,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131231424</v>
+        <v>131231469</v>
       </c>
       <c r="B31" t="n">
         <v>80355</v>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449406</v>
+        <v>449689</v>
       </c>
       <c r="R31" t="n">
-        <v>6999460</v>
+        <v>6999668</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4619,6 +4619,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växer här på sälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4671,10 +4676,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131231469</v>
+        <v>131231275</v>
       </c>
       <c r="B32" t="n">
-        <v>80355</v>
+        <v>79250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4682,21 +4687,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4709,10 +4714,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449689</v>
+        <v>449233</v>
       </c>
       <c r="R32" t="n">
-        <v>6999668</v>
+        <v>6999424</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4747,11 +4752,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Växer här på sälg.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4769,22 +4769,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131231430</v>
+        <v>131222457</v>
       </c>
       <c r="B34" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4943,40 +4943,47 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449758</v>
+        <v>449779</v>
       </c>
       <c r="R34" t="n">
-        <v>6999616</v>
+        <v>6999560</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5003,14 +5010,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med garnlavsbålar.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5019,7 +5036,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5040,12 +5056,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5063,10 +5079,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131222457</v>
+        <v>131231430</v>
       </c>
       <c r="B35" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5074,47 +5090,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åmyren, Åmyren, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449779</v>
+        <v>449758</v>
       </c>
       <c r="R35" t="n">
-        <v>6999560</v>
+        <v>6999616</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5141,24 +5150,14 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5167,6 +5166,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131231402</v>
+        <v>131231414</v>
       </c>
       <c r="B37" t="n">
-        <v>91818</v>
+        <v>57888</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5347,28 +5347,29 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5378,10 +5379,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449563</v>
+        <v>449386</v>
       </c>
       <c r="R37" t="n">
-        <v>6999529</v>
+        <v>6999458</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5416,13 +5417,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5461,10 +5466,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131231414</v>
+        <v>131231402</v>
       </c>
       <c r="B38" t="n">
-        <v>57888</v>
+        <v>91818</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5472,29 +5477,28 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5504,10 +5508,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>449386</v>
+        <v>449563</v>
       </c>
       <c r="R38" t="n">
-        <v>6999458</v>
+        <v>6999529</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5542,17 +5546,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131231429</v>
+        <v>131231470</v>
       </c>
       <c r="B41" t="n">
-        <v>79250</v>
+        <v>91838</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5853,26 +5853,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5880,10 +5880,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449725</v>
+        <v>449620</v>
       </c>
       <c r="R41" t="n">
-        <v>6999697</v>
+        <v>6999568</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5918,11 +5918,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlavsbålar.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5948,14 +5943,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5973,10 +5963,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131231470</v>
+        <v>131231429</v>
       </c>
       <c r="B42" t="n">
-        <v>91838</v>
+        <v>79250</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5984,26 +5974,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -6011,10 +6001,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449620</v>
+        <v>449725</v>
       </c>
       <c r="R42" t="n">
-        <v>6999568</v>
+        <v>6999697</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6049,6 +6039,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlavsbålar.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -6074,9 +6069,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -2741,10 +2741,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131231272</v>
+        <v>131231279</v>
       </c>
       <c r="B17" t="n">
-        <v>80356</v>
+        <v>79250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2752,21 +2752,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449248</v>
+        <v>449722</v>
       </c>
       <c r="R17" t="n">
-        <v>6999432</v>
+        <v>6999656</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2837,29 +2837,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2877,10 +2872,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131231464</v>
+        <v>131231272</v>
       </c>
       <c r="B18" t="n">
-        <v>91818</v>
+        <v>80356</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,30 +2883,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2919,10 +2910,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449494</v>
+        <v>449248</v>
       </c>
       <c r="R18" t="n">
-        <v>6999520</v>
+        <v>6999432</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2957,6 +2948,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2972,19 +2968,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3002,10 +3008,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131231279</v>
+        <v>131231464</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>91818</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3013,26 +3019,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3040,10 +3050,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449722</v>
+        <v>449494</v>
       </c>
       <c r="R19" t="n">
-        <v>6999656</v>
+        <v>6999520</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3078,11 +3088,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3108,14 +3113,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131231281</v>
+        <v>131231401</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>91818</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3662,26 +3662,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3689,10 +3693,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449569</v>
+        <v>449639</v>
       </c>
       <c r="R24" t="n">
-        <v>6999561</v>
+        <v>6999626</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3727,11 +3731,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3757,14 +3756,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3782,10 +3776,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131231282</v>
+        <v>131231399</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>91818</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3793,26 +3787,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3820,10 +3818,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449559</v>
+        <v>449456</v>
       </c>
       <c r="R25" t="n">
-        <v>6999502</v>
+        <v>6999489</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3883,14 +3881,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3908,10 +3901,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131231401</v>
+        <v>131231281</v>
       </c>
       <c r="B26" t="n">
-        <v>91818</v>
+        <v>79250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3919,30 +3912,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3950,10 +3939,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449639</v>
+        <v>449569</v>
       </c>
       <c r="R26" t="n">
-        <v>6999626</v>
+        <v>6999561</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3988,6 +3977,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -4013,9 +4007,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4033,10 +4032,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131231399</v>
+        <v>131231282</v>
       </c>
       <c r="B27" t="n">
-        <v>91818</v>
+        <v>79250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4044,30 +4043,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4075,10 +4070,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449456</v>
+        <v>449559</v>
       </c>
       <c r="R27" t="n">
-        <v>6999489</v>
+        <v>6999502</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4138,9 +4133,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131223307</v>
       </c>
       <c r="B2" t="n">
-        <v>92540</v>
+        <v>92543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131223087</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>131223402</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>131222541</v>
       </c>
       <c r="B5" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>131223136</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>131222821</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131223127</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131231273</v>
+        <v>131231420</v>
       </c>
       <c r="B9" t="n">
-        <v>80355</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1695,28 +1695,29 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1726,10 +1727,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449640</v>
+        <v>449719</v>
       </c>
       <c r="R9" t="n">
-        <v>6999605</v>
+        <v>6999549</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1766,7 +1767,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1775,7 +1776,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1784,29 +1784,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1824,39 +1814,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131231403</v>
+        <v>131231421</v>
       </c>
       <c r="B10" t="n">
-        <v>92540</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1866,10 +1857,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449444</v>
+        <v>449687</v>
       </c>
       <c r="R10" t="n">
-        <v>6999489</v>
+        <v>6999537</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1904,13 +1895,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1929,9 +1924,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1949,40 +1949,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131231420</v>
+        <v>131231403</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>92543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1992,10 +1991,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449719</v>
+        <v>449444</v>
       </c>
       <c r="R11" t="n">
-        <v>6999549</v>
+        <v>6999489</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2030,17 +2029,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2079,10 +2074,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131231421</v>
+        <v>131231273</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>80358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2090,29 +2085,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2122,10 +2116,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449687</v>
+        <v>449640</v>
       </c>
       <c r="R12" t="n">
-        <v>6999537</v>
+        <v>6999605</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2162,7 +2156,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2171,6 +2165,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2179,24 +2174,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2217,7 +2217,7 @@
         <v>131231276</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131231413</v>
+        <v>131231277</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2356,31 +2356,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2388,10 +2383,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449388</v>
+        <v>449771</v>
       </c>
       <c r="R14" t="n">
-        <v>6999459</v>
+        <v>6999558</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2428,7 +2423,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2437,6 +2432,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2457,12 +2453,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2480,10 +2476,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131231418</v>
+        <v>131231413</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2513,7 +2509,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2523,10 +2519,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449617</v>
+        <v>449388</v>
       </c>
       <c r="R15" t="n">
-        <v>6999646</v>
+        <v>6999459</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2563,7 +2559,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2590,9 +2586,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2610,10 +2611,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131231277</v>
+        <v>131231418</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2621,26 +2622,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2648,10 +2654,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449771</v>
+        <v>449617</v>
       </c>
       <c r="R16" t="n">
-        <v>6999558</v>
+        <v>6999646</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2688,7 +2694,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2697,7 +2703,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2716,14 +2721,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
         <v>131231279</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131231272</v>
+        <v>131231464</v>
       </c>
       <c r="B18" t="n">
-        <v>80356</v>
+        <v>91821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2883,26 +2883,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2910,10 +2914,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449248</v>
+        <v>449494</v>
       </c>
       <c r="R18" t="n">
-        <v>6999432</v>
+        <v>6999520</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2948,11 +2952,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2968,29 +2967,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3008,10 +2997,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131231464</v>
+        <v>131231272</v>
       </c>
       <c r="B19" t="n">
-        <v>91818</v>
+        <v>80359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3019,30 +3008,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3050,10 +3035,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449494</v>
+        <v>449248</v>
       </c>
       <c r="R19" t="n">
-        <v>6999520</v>
+        <v>6999432</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3088,6 +3073,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -3103,19 +3093,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3133,10 +3133,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131231280</v>
+        <v>131231426</v>
       </c>
       <c r="B20" t="n">
-        <v>79250</v>
+        <v>91841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3144,26 +3144,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449639</v>
+        <v>449572</v>
       </c>
       <c r="R20" t="n">
-        <v>6999579</v>
+        <v>6999535</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3209,11 +3209,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Gott om garnlavsbålar på flera gamla granar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3239,14 +3234,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3264,10 +3254,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131231278</v>
+        <v>131231280</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3302,10 +3292,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449763</v>
+        <v>449639</v>
       </c>
       <c r="R21" t="n">
-        <v>6999609</v>
+        <v>6999579</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3342,7 +3332,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Gott om garnlavsbålar på flera gamla granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3395,10 +3385,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131231426</v>
+        <v>131231278</v>
       </c>
       <c r="B22" t="n">
-        <v>91838</v>
+        <v>79253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3406,26 +3396,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3433,10 +3423,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449572</v>
+        <v>449763</v>
       </c>
       <c r="R22" t="n">
-        <v>6999535</v>
+        <v>6999609</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3471,6 +3461,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3496,9 +3491,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3519,7 +3519,7 @@
         <v>131231415</v>
       </c>
       <c r="B23" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>131231401</v>
       </c>
       <c r="B24" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>131231399</v>
       </c>
       <c r="B25" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>131231281</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>131231282</v>
       </c>
       <c r="B27" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>131231274</v>
       </c>
       <c r="B28" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>131231417</v>
       </c>
       <c r="B29" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>131231424</v>
       </c>
       <c r="B30" t="n">
-        <v>80355</v>
+        <v>80358</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4545,10 +4545,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131231469</v>
+        <v>131231275</v>
       </c>
       <c r="B31" t="n">
-        <v>80355</v>
+        <v>79253</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4556,21 +4556,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449689</v>
+        <v>449233</v>
       </c>
       <c r="R31" t="n">
-        <v>6999668</v>
+        <v>6999424</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4621,11 +4621,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Växer här på sälg.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4643,22 +4638,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4676,10 +4671,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131231275</v>
+        <v>131231469</v>
       </c>
       <c r="B32" t="n">
-        <v>79250</v>
+        <v>80358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4687,21 +4682,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4714,10 +4709,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449233</v>
+        <v>449689</v>
       </c>
       <c r="R32" t="n">
-        <v>6999424</v>
+        <v>6999668</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4752,6 +4747,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Växer här på sälg.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4769,22 +4769,22 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4805,7 +4805,7 @@
         <v>131231416</v>
       </c>
       <c r="B33" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131222457</v>
+        <v>131231430</v>
       </c>
       <c r="B34" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4943,47 +4943,40 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åmyren, Åmyren, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449779</v>
+        <v>449758</v>
       </c>
       <c r="R34" t="n">
-        <v>6999560</v>
+        <v>6999616</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5010,24 +5003,14 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5036,6 +5019,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5056,12 +5040,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5079,10 +5063,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131231430</v>
+        <v>131222457</v>
       </c>
       <c r="B35" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5090,40 +5074,47 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449758</v>
+        <v>449779</v>
       </c>
       <c r="R35" t="n">
-        <v>6999616</v>
+        <v>6999560</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5150,14 +5141,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med garnlavsbålar.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5166,7 +5167,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5213,7 +5213,7 @@
         <v>131231425</v>
       </c>
       <c r="B36" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5336,10 +5336,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131231414</v>
+        <v>131231402</v>
       </c>
       <c r="B37" t="n">
-        <v>57888</v>
+        <v>91821</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5347,29 +5347,28 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5379,10 +5378,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449386</v>
+        <v>449563</v>
       </c>
       <c r="R37" t="n">
-        <v>6999458</v>
+        <v>6999529</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5417,17 +5416,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5466,10 +5461,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131231402</v>
+        <v>131231414</v>
       </c>
       <c r="B38" t="n">
-        <v>91818</v>
+        <v>57891</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5477,28 +5472,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5508,10 +5504,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>449563</v>
+        <v>449386</v>
       </c>
       <c r="R38" t="n">
-        <v>6999529</v>
+        <v>6999458</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5546,13 +5542,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>131231400</v>
       </c>
       <c r="B39" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>131231423</v>
       </c>
       <c r="B40" t="n">
-        <v>79409</v>
+        <v>79412</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>131231470</v>
       </c>
       <c r="B41" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>131231429</v>
       </c>
       <c r="B42" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>131231471</v>
       </c>
       <c r="B43" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>131231422</v>
       </c>
       <c r="B44" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131223307</v>
       </c>
       <c r="B2" t="n">
-        <v>92543</v>
+        <v>92544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>131223087</v>
       </c>
       <c r="B3" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>131223402</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>131222541</v>
       </c>
       <c r="B5" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>131223136</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>131222821</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131223127</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>131231420</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>131231421</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>131231403</v>
       </c>
       <c r="B11" t="n">
-        <v>92543</v>
+        <v>92544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>131231273</v>
       </c>
       <c r="B12" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>131231276</v>
       </c>
       <c r="B13" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>131231277</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131231413</v>
+        <v>131231418</v>
       </c>
       <c r="B15" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449388</v>
+        <v>449617</v>
       </c>
       <c r="R15" t="n">
-        <v>6999459</v>
+        <v>6999646</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2586,14 +2586,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2611,10 +2606,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131231418</v>
+        <v>131231413</v>
       </c>
       <c r="B16" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2644,7 +2639,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2654,10 +2649,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449617</v>
+        <v>449388</v>
       </c>
       <c r="R16" t="n">
-        <v>6999646</v>
+        <v>6999459</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2694,7 +2689,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2721,9 +2716,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
         <v>131231279</v>
       </c>
       <c r="B17" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         <v>131231464</v>
       </c>
       <c r="B18" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
         <v>131231272</v>
       </c>
       <c r="B19" t="n">
-        <v>80359</v>
+        <v>80360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>131231426</v>
       </c>
       <c r="B20" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>131231280</v>
       </c>
       <c r="B21" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>131231278</v>
       </c>
       <c r="B22" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>131231415</v>
       </c>
       <c r="B23" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>131231401</v>
       </c>
       <c r="B24" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>131231399</v>
       </c>
       <c r="B25" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>131231281</v>
       </c>
       <c r="B26" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>131231282</v>
       </c>
       <c r="B27" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>131231274</v>
       </c>
       <c r="B28" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4292,7 +4292,7 @@
         <v>131231417</v>
       </c>
       <c r="B29" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131231424</v>
+        <v>131231275</v>
       </c>
       <c r="B30" t="n">
-        <v>80358</v>
+        <v>79254</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4430,21 +4430,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449406</v>
+        <v>449233</v>
       </c>
       <c r="R30" t="n">
-        <v>6999460</v>
+        <v>6999424</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4512,22 +4512,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4545,10 +4545,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131231275</v>
+        <v>131231424</v>
       </c>
       <c r="B31" t="n">
-        <v>79253</v>
+        <v>80359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4556,21 +4556,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4583,10 +4583,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449233</v>
+        <v>449406</v>
       </c>
       <c r="R31" t="n">
-        <v>6999424</v>
+        <v>6999460</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4638,22 +4638,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4674,7 +4674,7 @@
         <v>131231469</v>
       </c>
       <c r="B32" t="n">
-        <v>80358</v>
+        <v>80359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>131231416</v>
       </c>
       <c r="B33" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4935,7 +4935,7 @@
         <v>131231430</v>
       </c>
       <c r="B34" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>131222457</v>
       </c>
       <c r="B35" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>131231425</v>
       </c>
       <c r="B36" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>131231402</v>
       </c>
       <c r="B37" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>131231414</v>
       </c>
       <c r="B38" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>131231400</v>
       </c>
       <c r="B39" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>131231423</v>
       </c>
       <c r="B40" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131231470</v>
+        <v>131231429</v>
       </c>
       <c r="B41" t="n">
-        <v>91841</v>
+        <v>79254</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5853,26 +5853,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5880,10 +5880,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449620</v>
+        <v>449725</v>
       </c>
       <c r="R41" t="n">
-        <v>6999568</v>
+        <v>6999697</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5918,6 +5918,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlavsbålar.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5943,9 +5948,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5963,10 +5973,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131231429</v>
+        <v>131231471</v>
       </c>
       <c r="B42" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6001,10 +6011,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449725</v>
+        <v>449735</v>
       </c>
       <c r="R42" t="n">
-        <v>6999697</v>
+        <v>6999573</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6037,11 +6047,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6094,10 +6099,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131231471</v>
+        <v>131231422</v>
       </c>
       <c r="B43" t="n">
-        <v>79253</v>
+        <v>58051</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6105,37 +6110,50 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449735</v>
+        <v>449519</v>
       </c>
       <c r="R43" t="n">
-        <v>6999573</v>
+        <v>6999620</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6170,13 +6188,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -6185,24 +6207,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Med inslag av björk och sälg.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6220,10 +6227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131231422</v>
+        <v>131231470</v>
       </c>
       <c r="B44" t="n">
-        <v>58050</v>
+        <v>91842</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6231,50 +6238,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449519</v>
+        <v>449620</v>
       </c>
       <c r="R44" t="n">
-        <v>6999620</v>
+        <v>6999568</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6309,17 +6303,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6328,9 +6318,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Med inslag av björk och sälg.</t>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -1684,10 +1684,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131231420</v>
+        <v>131231273</v>
       </c>
       <c r="B9" t="n">
-        <v>57892</v>
+        <v>80359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1695,29 +1695,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1727,10 +1726,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449719</v>
+        <v>449640</v>
       </c>
       <c r="R9" t="n">
-        <v>6999549</v>
+        <v>6999605</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1767,7 +1766,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1776,6 +1775,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1784,19 +1784,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1814,7 +1824,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131231421</v>
+        <v>131231420</v>
       </c>
       <c r="B10" t="n">
         <v>57892</v>
@@ -1857,10 +1867,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>449687</v>
+        <v>449719</v>
       </c>
       <c r="R10" t="n">
-        <v>6999537</v>
+        <v>6999549</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1924,14 +1934,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1949,39 +1954,40 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131231403</v>
+        <v>131231421</v>
       </c>
       <c r="B11" t="n">
-        <v>92544</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1991,10 +1997,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449444</v>
+        <v>449687</v>
       </c>
       <c r="R11" t="n">
-        <v>6999489</v>
+        <v>6999537</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2029,13 +2035,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2054,9 +2064,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2074,39 +2089,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131231273</v>
+        <v>131231403</v>
       </c>
       <c r="B12" t="n">
-        <v>80359</v>
+        <v>92544</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2116,10 +2131,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449640</v>
+        <v>449444</v>
       </c>
       <c r="R12" t="n">
-        <v>6999605</v>
+        <v>6999489</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2154,11 +2169,6 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2174,29 +2184,19 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131231274</v>
+        <v>131231417</v>
       </c>
       <c r="B28" t="n">
-        <v>91842</v>
+        <v>57892</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4169,24 +4169,29 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4196,10 +4201,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449562</v>
+        <v>449423</v>
       </c>
       <c r="R28" t="n">
-        <v>6999557</v>
+        <v>6999465</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4236,7 +4241,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4245,7 +4250,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4264,14 +4268,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4289,10 +4288,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131231417</v>
+        <v>131231274</v>
       </c>
       <c r="B29" t="n">
-        <v>57892</v>
+        <v>91842</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4300,29 +4299,24 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4332,10 +4326,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449423</v>
+        <v>449562</v>
       </c>
       <c r="R29" t="n">
-        <v>6999465</v>
+        <v>6999557</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4372,7 +4366,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4381,6 +4375,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4399,9 +4394,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131231430</v>
+        <v>131222457</v>
       </c>
       <c r="B34" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4943,40 +4943,47 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449758</v>
+        <v>449779</v>
       </c>
       <c r="R34" t="n">
-        <v>6999616</v>
+        <v>6999560</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5003,14 +5010,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt med garnlavsbålar.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5019,7 +5036,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5040,12 +5056,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5063,10 +5079,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131222457</v>
+        <v>131231430</v>
       </c>
       <c r="B35" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5074,47 +5090,40 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Åmyren, Åmyren, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449779</v>
+        <v>449758</v>
       </c>
       <c r="R35" t="n">
-        <v>6999560</v>
+        <v>6999616</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -5141,24 +5150,14 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5167,6 +5166,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131223307</v>
+        <v>131231399</v>
       </c>
       <c r="B2" t="n">
-        <v>92552</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>teleomorf</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Byhögåsen, Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449158</v>
+        <v>449456</v>
       </c>
       <c r="R2" t="n">
-        <v>6999401</v>
+        <v>6999489</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,32 +750,18 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I en grov död gran i gammal granskog.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,14 +780,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131223087</v>
+        <v>131231400</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -828,47 +811,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Byhögåsen, Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449341</v>
+        <v>449460</v>
       </c>
       <c r="R3" t="n">
-        <v>6999446</v>
+        <v>6999564</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,32 +875,18 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -939,14 +905,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -964,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131223402</v>
+        <v>131231401</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,47 +936,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Byhögåsen, Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449138</v>
+        <v>449639</v>
       </c>
       <c r="R4" t="n">
-        <v>6999400</v>
+        <v>6999626</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1042,32 +1000,18 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs några meter på en grov gran vid kant mot ett hygge.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1086,14 +1030,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1111,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131223136</v>
+        <v>131231402</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1122,47 +1061,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Byhögåsen, Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449315</v>
+        <v>449563</v>
       </c>
       <c r="R5" t="n">
-        <v>6999445</v>
+        <v>6999529</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1189,32 +1125,18 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1233,14 +1155,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1258,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131222821</v>
+        <v>131231464</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,42 +1186,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Byhögåsen, Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449374</v>
+        <v>449494</v>
       </c>
       <c r="R6" t="n">
-        <v>6999458</v>
+        <v>6999520</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1331,32 +1250,18 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1375,14 +1280,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1400,48 +1300,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131222541</v>
+        <v>131231423</v>
       </c>
       <c r="B7" t="n">
-        <v>79261</v>
+        <v>79486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Byhögåsen, Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449710</v>
+        <v>449559</v>
       </c>
       <c r="R7" t="n">
-        <v>6999599</v>
+        <v>6999528</v>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1468,32 +1371,18 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På flera gamla granar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1514,12 +1403,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1537,10 +1426,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131223127</v>
+        <v>131231272</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1548,47 +1437,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Byhögåsen, Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449320</v>
+        <v>449248</v>
       </c>
       <c r="R8" t="n">
-        <v>6999445</v>
+        <v>6999432</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1615,24 +1497,14 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1641,6 +1513,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1649,24 +1522,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1684,55 +1562,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131231273</v>
+        <v>131223307</v>
       </c>
       <c r="B9" t="n">
-        <v>80369</v>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>449640</v>
+        <v>449158</v>
       </c>
       <c r="R9" t="n">
-        <v>6999605</v>
+        <v>6999401</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1759,14 +1635,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
+          <t>I en grov död gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1775,7 +1661,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1784,29 +1669,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1827,7 +1707,7 @@
         <v>131231403</v>
       </c>
       <c r="B10" t="n">
-        <v>92555</v>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1949,56 +1829,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131231420</v>
+        <v>131222541</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>449719</v>
+        <v>449710</v>
       </c>
       <c r="R11" t="n">
-        <v>6999549</v>
+        <v>6999599</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2025,14 +1897,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>På flera gamla granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2059,9 +1941,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2079,42 +1966,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131231421</v>
+        <v>131231275</v>
       </c>
       <c r="B12" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2122,10 +2004,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449687</v>
+        <v>449233</v>
       </c>
       <c r="R12" t="n">
-        <v>6999537</v>
+        <v>6999424</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2160,17 +2042,13 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2191,12 +2069,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2214,14 +2092,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131231277</v>
+        <v>131231276</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2252,10 +2130,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449771</v>
+        <v>449610</v>
       </c>
       <c r="R13" t="n">
-        <v>6999558</v>
+        <v>6999650</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2292,7 +2170,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Gott om garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2345,14 +2223,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131231276</v>
+        <v>131231277</v>
       </c>
       <c r="B14" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2383,10 +2261,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449610</v>
+        <v>449771</v>
       </c>
       <c r="R14" t="n">
-        <v>6999650</v>
+        <v>6999558</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2423,7 +2301,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gott om garnlav på flera granar.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2476,42 +2354,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131231413</v>
+        <v>131231278</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2519,10 +2392,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449388</v>
+        <v>449763</v>
       </c>
       <c r="R15" t="n">
-        <v>6999459</v>
+        <v>6999609</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2559,7 +2432,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2568,6 +2441,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2588,12 +2462,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2611,42 +2485,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131231418</v>
+        <v>131231279</v>
       </c>
       <c r="B16" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2654,10 +2523,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449617</v>
+        <v>449722</v>
       </c>
       <c r="R16" t="n">
-        <v>6999646</v>
+        <v>6999656</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2694,7 +2563,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2703,6 +2572,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2721,9 +2591,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2741,41 +2616,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131231464</v>
+        <v>131231280</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2783,10 +2654,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>449494</v>
+        <v>449639</v>
       </c>
       <c r="R17" t="n">
-        <v>6999520</v>
+        <v>6999579</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2821,6 +2692,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gott om garnlavsbålar på flera gamla granar.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2846,9 +2722,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2866,32 +2747,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131231272</v>
+        <v>131231281</v>
       </c>
       <c r="B18" t="n">
-        <v>80370</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2904,10 +2785,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449248</v>
+        <v>449569</v>
       </c>
       <c r="R18" t="n">
-        <v>6999432</v>
+        <v>6999561</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2944,7 +2825,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Här växer skrovellav på en böjd gammal sälg som står ca 10 m söder om en nyligen avverkad yta inom avverkningsanmälan A 63463-2025. Avverkningen på denna plats har sannolikt utförts illegalt av SCA inom ett aktivt revir för tretåig hackspett.</t>
+          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2962,29 +2843,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Gammal granskog med inslag av björk och sälg.</t>
-        </is>
-      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3002,14 +2878,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131231279</v>
+        <v>131231282</v>
       </c>
       <c r="B19" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -3040,10 +2916,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449722</v>
+        <v>449559</v>
       </c>
       <c r="R19" t="n">
-        <v>6999656</v>
+        <v>6999502</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3076,11 +2952,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3133,37 +3004,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131231426</v>
+        <v>131231429</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3171,10 +3042,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449572</v>
+        <v>449725</v>
       </c>
       <c r="R20" t="n">
-        <v>6999535</v>
+        <v>6999697</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3209,6 +3080,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlavsbålar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3234,9 +3110,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3254,14 +3135,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131231280</v>
+        <v>131231430</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3292,10 +3173,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449639</v>
+        <v>449758</v>
       </c>
       <c r="R21" t="n">
-        <v>6999579</v>
+        <v>6999616</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3332,7 +3213,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gott om garnlavsbålar på flera gamla granar.</t>
+          <t>Rikligt med garnlavsbålar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3385,14 +3266,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131231278</v>
+        <v>131231471</v>
       </c>
       <c r="B22" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3423,10 +3304,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449763</v>
+        <v>449735</v>
       </c>
       <c r="R22" t="n">
-        <v>6999609</v>
+        <v>6999573</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3459,11 +3340,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3516,10 +3392,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131231415</v>
+        <v>131231273</v>
       </c>
       <c r="B23" t="n">
-        <v>57902</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3527,29 +3403,28 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3559,10 +3434,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449394</v>
+        <v>449640</v>
       </c>
       <c r="R23" t="n">
-        <v>6999468</v>
+        <v>6999605</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3599,7 +3474,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på gran.</t>
+          <t>Ymnigt med lunglav längs flera meter på en gammal flerstammig sälg. Här finns gott om både äldre och yngre bålar. Helt klart en indikation på skog med höga naturvärden!</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3608,6 +3483,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3616,24 +3492,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Gammal granskog med inslag av björk och sälg.</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3651,10 +3532,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131231282</v>
+        <v>131231424</v>
       </c>
       <c r="B24" t="n">
-        <v>79264</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3662,21 +3543,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3689,10 +3570,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449559</v>
+        <v>449406</v>
       </c>
       <c r="R24" t="n">
-        <v>6999502</v>
+        <v>6999460</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3744,22 +3625,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3777,10 +3658,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131231401</v>
+        <v>131231469</v>
       </c>
       <c r="B25" t="n">
-        <v>91832</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3788,30 +3669,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3819,10 +3696,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>449639</v>
+        <v>449689</v>
       </c>
       <c r="R25" t="n">
-        <v>6999626</v>
+        <v>6999668</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3857,6 +3734,11 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Växer här på sälg.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3874,17 +3756,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3902,10 +3789,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131231399</v>
+        <v>131222457</v>
       </c>
       <c r="B26" t="n">
-        <v>91832</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3913,44 +3800,47 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Åmyren, Åmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449456</v>
+        <v>449779</v>
       </c>
       <c r="R26" t="n">
-        <v>6999489</v>
+        <v>6999560</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3977,18 +3867,32 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -4007,9 +3911,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4027,10 +3936,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131231281</v>
+        <v>131222821</v>
       </c>
       <c r="B27" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4038,40 +3947,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449569</v>
+        <v>449374</v>
       </c>
       <c r="R27" t="n">
-        <v>6999561</v>
+        <v>6999458</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4098,14 +4009,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar. Hyfsat rikligt.</t>
+          <t>Ringhack, färska, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4114,7 +4035,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4135,12 +4055,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4158,10 +4078,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131231274</v>
+        <v>131223087</v>
       </c>
       <c r="B28" t="n">
-        <v>91852</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4169,40 +4089,47 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449562</v>
+        <v>449341</v>
       </c>
       <c r="R28" t="n">
-        <v>6999557</v>
+        <v>6999446</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4229,14 +4156,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4245,7 +4182,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4289,10 +4225,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131231417</v>
+        <v>131223127</v>
       </c>
       <c r="B29" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4318,27 +4254,29 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449423</v>
+        <v>449320</v>
       </c>
       <c r="R29" t="n">
-        <v>6999465</v>
+        <v>6999445</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4365,14 +4303,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4399,9 +4347,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4419,10 +4372,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131231424</v>
+        <v>131223136</v>
       </c>
       <c r="B30" t="n">
-        <v>80369</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4430,40 +4383,47 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>449406</v>
+        <v>449315</v>
       </c>
       <c r="R30" t="n">
-        <v>6999460</v>
+        <v>6999445</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4490,18 +4450,32 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4512,22 +4486,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4545,10 +4519,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131231469</v>
+        <v>131223402</v>
       </c>
       <c r="B31" t="n">
-        <v>80369</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4556,40 +4530,47 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Byhögåsen, Jmt</t>
+          <t>Byhögåsen, Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>449689</v>
+        <v>449138</v>
       </c>
       <c r="R31" t="n">
-        <v>6999668</v>
+        <v>6999400</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4616,14 +4597,24 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Växer här på sälg.</t>
+          <t>Ringhack, färska, längs några meter på en grov gran vid kant mot ett hygge.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4632,7 +4623,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4643,22 +4633,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4676,10 +4666,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131231416</v>
+        <v>131231413</v>
       </c>
       <c r="B32" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4709,7 +4699,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4719,10 +4709,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>449456</v>
+        <v>449388</v>
       </c>
       <c r="R32" t="n">
-        <v>6999484</v>
+        <v>6999459</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4759,7 +4749,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på gran.</t>
+          <t>Ringhack, färska, på gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4786,9 +4776,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4806,10 +4801,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131231275</v>
+        <v>131231414</v>
       </c>
       <c r="B33" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4817,26 +4812,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449233</v>
+        <v>449386</v>
       </c>
       <c r="R33" t="n">
-        <v>6999424</v>
+        <v>6999458</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4882,13 +4882,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4907,14 +4911,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4932,10 +4931,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131222457</v>
+        <v>131231415</v>
       </c>
       <c r="B34" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4961,29 +4960,27 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Åmyren, Åmyren, Jmt</t>
+          <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449779</v>
+        <v>449394</v>
       </c>
       <c r="R34" t="n">
-        <v>6999560</v>
+        <v>6999468</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -5010,24 +5007,14 @@
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, längs några meter på en gran vid kant mot yngre skog.</t>
+          <t>Ringhack, färska och äldre, på gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5079,10 +5066,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131231430</v>
+        <v>131231416</v>
       </c>
       <c r="B35" t="n">
-        <v>79264</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5090,26 +5077,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5117,10 +5109,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449758</v>
+        <v>449456</v>
       </c>
       <c r="R35" t="n">
-        <v>6999616</v>
+        <v>6999484</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5157,7 +5149,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Rikligt med garnlavsbålar.</t>
+          <t>Ringhack, äldre, på gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5166,7 +5158,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -5185,14 +5176,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5210,10 +5196,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131231425</v>
+        <v>131231417</v>
       </c>
       <c r="B36" t="n">
-        <v>91852</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5221,24 +5207,29 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5248,10 +5239,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449457</v>
+        <v>449423</v>
       </c>
       <c r="R36" t="n">
-        <v>6999561</v>
+        <v>6999465</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5286,13 +5277,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5311,14 +5306,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5336,10 +5326,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131231414</v>
+        <v>131231418</v>
       </c>
       <c r="B37" t="n">
-        <v>57902</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5379,10 +5369,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>449386</v>
+        <v>449617</v>
       </c>
       <c r="R37" t="n">
-        <v>6999458</v>
+        <v>6999646</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5466,10 +5456,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131231402</v>
+        <v>131231420</v>
       </c>
       <c r="B38" t="n">
-        <v>91832</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5477,28 +5467,29 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5508,10 +5499,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>449563</v>
+        <v>449719</v>
       </c>
       <c r="R38" t="n">
-        <v>6999529</v>
+        <v>6999549</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5546,13 +5537,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5591,10 +5586,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131231400</v>
+        <v>131231421</v>
       </c>
       <c r="B39" t="n">
-        <v>91832</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5602,28 +5597,29 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5633,10 +5629,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>449460</v>
+        <v>449687</v>
       </c>
       <c r="R39" t="n">
-        <v>6999564</v>
+        <v>6999537</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5671,13 +5667,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5696,9 +5696,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5716,37 +5721,42 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131231423</v>
+        <v>131231467</v>
       </c>
       <c r="B40" t="n">
-        <v>79423</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5754,10 +5764,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>449559</v>
+        <v>449370</v>
       </c>
       <c r="R40" t="n">
-        <v>6999528</v>
+        <v>6999447</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5792,13 +5802,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5817,14 +5831,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5842,10 +5851,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131231470</v>
+        <v>131231422</v>
       </c>
       <c r="B41" t="n">
-        <v>91852</v>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5853,37 +5862,50 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Byhögåsen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449620</v>
+        <v>449519</v>
       </c>
       <c r="R41" t="n">
-        <v>6999568</v>
+        <v>6999620</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5918,13 +5940,17 @@
           <t>2026-02-19</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5933,19 +5959,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Med inslag av björk och sälg.</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5960,391 +5976,6 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>131231429</v>
-      </c>
-      <c r="B42" t="n">
-        <v>79264</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Byhögåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>449725</v>
-      </c>
-      <c r="R42" t="n">
-        <v>6999697</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlavsbålar.</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>131231471</v>
-      </c>
-      <c r="B43" t="n">
-        <v>79264</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Byhögåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>449735</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6999573</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>131231422</v>
-      </c>
-      <c r="B44" t="n">
-        <v>58061</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Byhögåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>449519</v>
-      </c>
-      <c r="R44" t="n">
-        <v>6999620</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Hallen</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Synobservation av 2 st talltitor i flerskiktad gammal granskog med förekomst av murknande björkhögstubbar för talltitans bohål. Här finns granskog med absolut höga naturvärden!</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>Med inslag av björk och sälg.</t>
-        </is>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63463-2025 artfynd.xlsx
+++ b/artfynd/A 63463-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231399</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231400</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231401</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1172,6 +1192,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231402</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1297,6 +1322,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231464</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1423,6 +1453,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231423</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1559,6 +1594,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231272</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1701,6 +1741,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223307</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1826,6 +1871,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231403</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1963,6 +2013,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131222541</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2089,6 +2144,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231275</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2220,6 +2280,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231276</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2351,6 +2416,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231277</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2482,6 +2552,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231278</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2613,6 +2688,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231279</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2744,6 +2824,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231280</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2875,6 +2960,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231281</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3001,6 +3091,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231282</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3132,6 +3227,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231429</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3263,6 +3363,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231430</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3389,6 +3494,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231471</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3529,6 +3639,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231273</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3655,6 +3770,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231424</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3786,6 +3906,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231469</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3933,6 +4058,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131222457</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4075,6 +4205,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131222821</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4222,6 +4357,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223087</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4369,6 +4509,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223127</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4516,6 +4661,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223136</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4663,6 +4813,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131223402</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4798,6 +4953,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231413</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4928,6 +5088,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231414</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5063,6 +5228,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231415</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5193,6 +5363,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231416</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5323,6 +5498,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231417</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5453,6 +5633,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231418</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5583,6 +5768,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231420</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5718,6 +5908,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231421</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5848,6 +6043,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231467</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5976,8 +6176,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131231422</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>